--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="137">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -237,6 +237,9 @@
   </si>
   <si>
     <t>2026-09-20T11:24:59.812151Z</t>
+  </si>
+  <si>
+    <t>2026-09-20T14:29:08.384484Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1761,7 +1764,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1833,8 +1836,37 @@
         <v>371.38</v>
       </c>
     </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="C4" s="6">
+        <v>2.31</v>
+      </c>
+      <c r="D4" s="6">
+        <v>400.86</v>
+      </c>
+      <c r="E4" s="6">
+        <v>424.3797912597656</v>
+      </c>
+      <c r="F4" s="6">
+        <v>2.458150386810303</v>
+      </c>
+      <c r="G4" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H4" s="6">
+        <v>-10.08</v>
+      </c>
+      <c r="I4" s="6">
+        <v>369.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I3"/>
+  <autoFilter ref="A2:I4"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1856,7 +1888,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1871,39 +1903,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1929,17 +1961,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1947,134 +1979,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>93</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2082,10 +2114,10 @@
         <v>44</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2093,56 +2125,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="138">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>2026-09-20T14:29:08.384484Z</t>
+  </si>
+  <si>
+    <t>2026-09-20T17:40:29.109590Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1764,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1865,8 +1868,31 @@
         <v>369.83</v>
       </c>
     </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="6">
+        <v>461.2220458984375</v>
+      </c>
+      <c r="F5" s="6">
+        <v>5.188785552978516</v>
+      </c>
+      <c r="G5" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H5" s="6">
+        <v>-10.08</v>
+      </c>
+      <c r="I5" s="6">
+        <v>369.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I4"/>
+  <autoFilter ref="A2:I5"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1888,7 +1914,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1903,39 +1929,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1961,17 +1987,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -1979,134 +2005,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2114,10 +2140,10 @@
         <v>44</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2125,56 +2151,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="139">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>2026-09-20T17:40:29.109590Z</t>
+  </si>
+  <si>
+    <t>2026-09-20T19:44:30.991650Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1767,7 +1770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1891,8 +1894,37 @@
         <v>369.83</v>
       </c>
     </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="C6" s="6">
+        <v>2.92</v>
+      </c>
+      <c r="D6" s="6">
+        <v>404.97</v>
+      </c>
+      <c r="E6" s="6">
+        <v>443.4601745605469</v>
+      </c>
+      <c r="F6" s="6">
+        <v>14.24276256561279</v>
+      </c>
+      <c r="G6" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H6" s="6">
+        <v>-9.98</v>
+      </c>
+      <c r="I6" s="6">
+        <v>370.48</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I5"/>
+  <autoFilter ref="A2:I6"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1914,7 +1946,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1929,39 +1961,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -1987,17 +2019,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2005,134 +2037,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>95</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2140,10 +2172,10 @@
         <v>44</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2151,56 +2183,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="140">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -246,6 +246,9 @@
   </si>
   <si>
     <t>2026-09-20T19:44:30.991650Z</t>
+  </si>
+  <si>
+    <t>2026-09-20T22:42:30.172509Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1770,7 +1773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1923,8 +1926,31 @@
         <v>370.48</v>
       </c>
     </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="6">
+        <v>173.0411529541016</v>
+      </c>
+      <c r="F7" s="6">
+        <v>9.643379211425781</v>
+      </c>
+      <c r="G7" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H7" s="6">
+        <v>-10.01</v>
+      </c>
+      <c r="I7" s="6">
+        <v>369.6</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I6"/>
+  <autoFilter ref="A2:I7"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1946,7 +1972,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1961,39 +1987,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2019,17 +2045,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2037,134 +2063,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2172,10 +2198,10 @@
         <v>44</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2183,56 +2209,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$7</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="141">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>2026-09-20T22:42:30.172509Z</t>
+  </si>
+  <si>
+    <t>2026-09-21T00:31:17.024499Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1773,7 +1776,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1949,8 +1952,35 @@
         <v>369.6</v>
       </c>
     </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="4"/>
+      <c r="C8" s="6">
+        <v>0.4</v>
+      </c>
+      <c r="D8" s="6">
+        <v>349.46</v>
+      </c>
+      <c r="E8" s="6">
+        <v>261.2619934082031</v>
+      </c>
+      <c r="F8" s="6">
+        <v>5.218446731567383</v>
+      </c>
+      <c r="G8" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H8" s="6">
+        <v>-10.82</v>
+      </c>
+      <c r="I8" s="6">
+        <v>355.79</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I7"/>
+  <autoFilter ref="A2:I8"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -1972,7 +2002,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1987,39 +2017,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2045,17 +2075,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2063,134 +2093,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2198,10 +2228,10 @@
         <v>44</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2209,56 +2239,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -13,15 +13,15 @@
     <sheet name="Method_Legend" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="144">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -101,33 +101,42 @@
     <t>Source</t>
   </si>
   <si>
+    <t>2026-09-21T04:50:00Z</t>
+  </si>
+  <si>
+    <t>GOES-19</t>
+  </si>
+  <si>
+    <t>product/data</t>
+  </si>
+  <si>
+    <t>anomaly/outage</t>
+  </si>
+  <si>
+    <t>PRODUCT_DATA</t>
+  </si>
+  <si>
+    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
+  </si>
+  <si>
+    <t>Product Anomaly/Outage: GOES-19 Aerosol, Cloud, and Land Meso-2 products-Issued: September 21, 2026 0450Z</t>
+  </si>
+  <si>
+    <t>Temporal association only; causality NOT established.</t>
+  </si>
+  <si>
+    <t>NOAA OSPO satellite messages</t>
+  </si>
+  <si>
     <t>2026-09-14T14:25:00Z</t>
   </si>
   <si>
     <t>GOES-18, GOES-19</t>
   </si>
   <si>
-    <t>product/data</t>
-  </si>
-  <si>
-    <t>anomaly/outage</t>
-  </si>
-  <si>
-    <t>PRODUCT_DATA</t>
-  </si>
-  <si>
-    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
-  </si>
-  <si>
     <t>Product Anomaly/Outage: Impact to GOES-18, GOES-19, and SOLAR-1 Products Issued: September 14, 2026 1425Z</t>
   </si>
   <si>
-    <t>Temporal association only; causality NOT established.</t>
-  </si>
-  <si>
-    <t>NOAA OSPO satellite messages</t>
-  </si>
-  <si>
     <t>2026-09-14T14:18:00Z</t>
   </si>
   <si>
@@ -149,9 +158,6 @@
     <t>2026-09-08T18:10:00Z</t>
   </si>
   <si>
-    <t>GOES-19</t>
-  </si>
-  <si>
     <t>instrument/product</t>
   </si>
   <si>
@@ -252,6 +258,9 @@
   </si>
   <si>
     <t>2026-09-21T00:31:17.024499Z</t>
+  </si>
+  <si>
+    <t>2026-09-21T05:29:07.960381Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -974,7 +983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X15"/>
+  <dimension ref="A1:X16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1138,30 +1147,48 @@
       <c r="G4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="6">
-        <v>4</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="J4" s="6">
+        <v>365.54</v>
+      </c>
+      <c r="K4" s="6">
+        <v>287.3075561523438</v>
+      </c>
+      <c r="L4" s="6">
+        <v>0.6605671048164368</v>
+      </c>
       <c r="M4" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="N4" s="4"/>
-      <c r="O4" s="4"/>
+        <v>1.67</v>
+      </c>
+      <c r="N4" s="6">
+        <v>-2.1</v>
+      </c>
+      <c r="O4" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="P4" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q4" s="6">
+        <v>-4.05</v>
+      </c>
+      <c r="R4" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="S4" s="6">
         <v>3</v>
       </c>
-      <c r="T4" s="4"/>
-      <c r="U4" s="4"/>
+      <c r="T4" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="U4" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="V4" s="6">
-        <v>5.8</v>
+        <v>39.8</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>33</v>
@@ -1175,7 +1202,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>28</v>
@@ -1190,7 +1217,7 @@
         <v>31</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" s="6">
         <v>4</v>
@@ -1226,10 +1253,10 @@
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -1244,7 +1271,7 @@
         <v>31</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="6">
         <v>4</v>
@@ -1280,10 +1307,10 @@
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>28</v>
@@ -1298,7 +1325,7 @@
         <v>31</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H7" s="6">
         <v>4</v>
@@ -1334,50 +1361,50 @@
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>44</v>
+      <c r="E8" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H8" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="6">
-        <v>4.67</v>
+        <v>2.67</v>
       </c>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
       <c r="P8" s="6">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="Q8" s="4"/>
       <c r="R8" s="4"/>
       <c r="S8" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T8" s="4"/>
       <c r="U8" s="4"/>
       <c r="V8" s="6">
-        <v>17.5</v>
+        <v>5.8</v>
       </c>
       <c r="W8" s="4" t="s">
         <v>33</v>
@@ -1388,19 +1415,19 @@
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>31</v>
@@ -1445,16 +1472,16 @@
         <v>48</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>31</v>
@@ -1463,7 +1490,7 @@
         <v>49</v>
       </c>
       <c r="H10" s="6">
-        <v>4.67</v>
+        <v>3</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
@@ -1499,47 +1526,47 @@
         <v>50</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>51</v>
+        <v>27</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="5" t="s">
-        <v>30</v>
+      <c r="E11" s="7" t="s">
+        <v>46</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11" s="6">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="6">
-        <v>0.33</v>
+        <v>4.67</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
       <c r="V11" s="6">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="W11" s="4" t="s">
         <v>33</v>
@@ -1550,10 +1577,10 @@
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>53</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>51</v>
       </c>
       <c r="C12" s="4" t="s">
         <v>28</v>
@@ -1571,7 +1598,7 @@
         <v>54</v>
       </c>
       <c r="H12" s="6">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
@@ -1607,7 +1634,7 @@
         <v>55</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>28</v>
@@ -1625,19 +1652,19 @@
         <v>56</v>
       </c>
       <c r="H13" s="6">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="6">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="6">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
@@ -1661,7 +1688,7 @@
         <v>57</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>28</v>
@@ -1686,7 +1713,7 @@
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="6">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
@@ -1715,16 +1742,16 @@
         <v>59</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="7" t="s">
-        <v>44</v>
+      <c r="E15" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>31</v>
@@ -1733,7 +1760,7 @@
         <v>60</v>
       </c>
       <c r="H15" s="6">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1764,8 +1791,62 @@
         <v>34</v>
       </c>
     </row>
+    <row r="16" spans="1:24">
+      <c r="A16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H16" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
+      <c r="M16" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="N16" s="4"/>
+      <c r="O16" s="4"/>
+      <c r="P16" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="Q16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4"/>
+      <c r="V16" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="W16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X16" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:X15"/>
+  <autoFilter ref="A3:X16"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A2:X2"/>
@@ -1776,7 +1857,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1785,7 +1866,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1798,36 +1879,36 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1850,7 +1931,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B4" s="6">
         <v>0.67</v>
@@ -1879,7 +1960,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -1902,7 +1983,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B6" s="6">
         <v>0.33</v>
@@ -1931,7 +2012,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -1954,7 +2035,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="6">
@@ -1979,8 +2060,37 @@
         <v>355.79</v>
       </c>
     </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+      <c r="D9" s="6">
+        <v>365.54</v>
+      </c>
+      <c r="E9" s="6">
+        <v>287.3075561523438</v>
+      </c>
+      <c r="F9" s="6">
+        <v>0.6605671048164368</v>
+      </c>
+      <c r="G9" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H9" s="6">
+        <v>-10.69</v>
+      </c>
+      <c r="I9" s="6">
+        <v>390.18</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I8"/>
+  <autoFilter ref="A2:I9"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2002,7 +2112,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2017,39 +2127,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2075,17 +2185,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2093,145 +2203,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2239,56 +2349,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="242" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="145">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>2026-09-21T05:29:07.960381Z</t>
+  </si>
+  <si>
+    <t>2026-09-21T11:06:31.680365Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1857,7 +1860,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2089,8 +2092,31 @@
         <v>390.18</v>
       </c>
     </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="6">
+        <v>322.1436157226562</v>
+      </c>
+      <c r="F10" s="6">
+        <v>0.732627272605896</v>
+      </c>
+      <c r="G10" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H10" s="6">
+        <v>-10.69</v>
+      </c>
+      <c r="I10" s="6">
+        <v>390.18</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I9"/>
+  <autoFilter ref="A2:I10"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2112,7 +2138,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2127,39 +2153,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2185,17 +2211,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2203,134 +2229,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>101</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2338,10 +2364,10 @@
         <v>46</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2349,56 +2375,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="146">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>2026-09-21T11:06:31.680365Z</t>
+  </si>
+  <si>
+    <t>2026-09-21T17:16:13.398936Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1150,12 +1153,14 @@
       <c r="G4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="6">
+        <v>0.33</v>
+      </c>
       <c r="I4" s="6">
-        <v>-0.6899999999999999</v>
+        <v>-0.66</v>
       </c>
       <c r="J4" s="6">
-        <v>365.54</v>
+        <v>354.3</v>
       </c>
       <c r="K4" s="6">
         <v>287.3075561523438</v>
@@ -1167,7 +1172,7 @@
         <v>1.67</v>
       </c>
       <c r="N4" s="6">
-        <v>-2.1</v>
+        <v>-2.11</v>
       </c>
       <c r="O4" s="6">
         <v>594.5599999999999</v>
@@ -1860,7 +1865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2115,8 +2120,31 @@
         <v>390.18</v>
       </c>
     </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="6">
+        <v>564.8268432617188</v>
+      </c>
+      <c r="F11" s="6">
+        <v>8.707561492919922</v>
+      </c>
+      <c r="G11" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H11" s="6">
+        <v>-10.51</v>
+      </c>
+      <c r="I11" s="6">
+        <v>382.03</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I10"/>
+  <autoFilter ref="A2:I11"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2138,7 +2166,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2153,39 +2181,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2211,17 +2239,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2229,134 +2257,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>102</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2364,10 +2392,10 @@
         <v>46</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2375,56 +2403,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="147">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -267,6 +267,9 @@
   </si>
   <si>
     <t>2026-09-21T17:16:13.398936Z</t>
+  </si>
+  <si>
+    <t>2026-09-21T21:17:30.794616Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1157,7 +1160,7 @@
         <v>0.33</v>
       </c>
       <c r="I4" s="6">
-        <v>-0.66</v>
+        <v>0.17</v>
       </c>
       <c r="J4" s="6">
         <v>354.3</v>
@@ -1172,7 +1175,7 @@
         <v>1.67</v>
       </c>
       <c r="N4" s="6">
-        <v>-2.11</v>
+        <v>-2.1</v>
       </c>
       <c r="O4" s="6">
         <v>594.5599999999999</v>
@@ -1865,7 +1868,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2143,8 +2146,35 @@
         <v>382.03</v>
       </c>
     </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="4"/>
+      <c r="C12" s="6">
+        <v>-3.28</v>
+      </c>
+      <c r="D12" s="6">
+        <v>359.57</v>
+      </c>
+      <c r="E12" s="6">
+        <v>352.4024963378906</v>
+      </c>
+      <c r="F12" s="6">
+        <v>14.14668369293213</v>
+      </c>
+      <c r="G12" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H12" s="6">
+        <v>-10.71</v>
+      </c>
+      <c r="I12" s="6">
+        <v>382.24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I11"/>
+  <autoFilter ref="A2:I12"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2166,7 +2196,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2181,39 +2211,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2239,17 +2269,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2257,134 +2287,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2392,10 +2422,10 @@
         <v>46</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2403,56 +2433,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="148">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -270,6 +270,9 @@
   </si>
   <si>
     <t>2026-09-21T21:17:30.794616Z</t>
+  </si>
+  <si>
+    <t>2026-09-22T00:17:40.109948Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1160,7 +1163,7 @@
         <v>0.33</v>
       </c>
       <c r="I4" s="6">
-        <v>0.17</v>
+        <v>-0.66</v>
       </c>
       <c r="J4" s="6">
         <v>354.3</v>
@@ -1175,7 +1178,7 @@
         <v>1.67</v>
       </c>
       <c r="N4" s="6">
-        <v>-2.1</v>
+        <v>-2.11</v>
       </c>
       <c r="O4" s="6">
         <v>594.5599999999999</v>
@@ -1868,7 +1871,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2173,8 +2176,37 @@
         <v>382.24</v>
       </c>
     </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-2.19</v>
+      </c>
+      <c r="D13" s="6">
+        <v>328.3</v>
+      </c>
+      <c r="E13" s="6">
+        <v>318.7031555175781</v>
+      </c>
+      <c r="F13" s="6">
+        <v>4.57482385635376</v>
+      </c>
+      <c r="G13" s="6">
+        <v>2</v>
+      </c>
+      <c r="H13" s="6">
+        <v>-11.95</v>
+      </c>
+      <c r="I13" s="6">
+        <v>387.2</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I12"/>
+  <autoFilter ref="A2:I13"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2196,7 +2228,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2211,39 +2243,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2269,17 +2301,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2287,134 +2319,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2422,10 +2454,10 @@
         <v>46</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2433,56 +2465,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="149">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>2026-09-22T00:17:40.109948Z</t>
+  </si>
+  <si>
+    <t>2026-09-22T05:22:45.138014Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1871,7 +1874,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2205,8 +2208,37 @@
         <v>387.2</v>
       </c>
     </row>
+    <row r="14" spans="1:9">
+      <c r="A14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="6">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6">
+        <v>2.23</v>
+      </c>
+      <c r="D14" s="6">
+        <v>353.71</v>
+      </c>
+      <c r="E14" s="6">
+        <v>361.6636657714844</v>
+      </c>
+      <c r="F14" s="6">
+        <v>0.5141282081604004</v>
+      </c>
+      <c r="G14" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H14" s="6">
+        <v>-10.84</v>
+      </c>
+      <c r="I14" s="6">
+        <v>387.31</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I13"/>
+  <autoFilter ref="A2:I14"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2228,7 +2260,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2243,39 +2275,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2301,17 +2333,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2319,134 +2351,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>105</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2454,10 +2486,10 @@
         <v>46</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2465,56 +2497,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="247" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="150">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -276,6 +276,9 @@
   </si>
   <si>
     <t>2026-09-22T05:22:45.138014Z</t>
+  </si>
+  <si>
+    <t>2026-09-22T10:20:32.345810Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1874,7 +1877,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2237,8 +2240,31 @@
         <v>387.31</v>
       </c>
     </row>
+    <row r="15" spans="1:9">
+      <c r="A15" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="6">
+        <v>122.2937545776367</v>
+      </c>
+      <c r="F15" s="6">
+        <v>0.5407330989837646</v>
+      </c>
+      <c r="G15" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H15" s="6">
+        <v>-10.64</v>
+      </c>
+      <c r="I15" s="6">
+        <v>387.31</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I14"/>
+  <autoFilter ref="A2:I15"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2260,7 +2286,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2275,39 +2301,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2333,17 +2359,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2351,134 +2377,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2486,10 +2512,10 @@
         <v>46</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2497,56 +2523,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -13,15 +13,15 @@
     <sheet name="Method_Legend" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="155">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -101,33 +101,48 @@
     <t>Source</t>
   </si>
   <si>
+    <t>2026-09-22T14:15:00Z</t>
+  </si>
+  <si>
+    <t>GOES-18</t>
+  </si>
+  <si>
+    <t>product/data</t>
+  </si>
+  <si>
+    <t>anomaly/outage</t>
+  </si>
+  <si>
+    <t>PRODUCT_DATA</t>
+  </si>
+  <si>
+    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
+  </si>
+  <si>
+    <t>Product Anomaly/Outage: Update #1 - GOES-18/19 Product Distribution Outage, Issued: September 22, 2026 1415 UTC</t>
+  </si>
+  <si>
+    <t>Temporal association only; causality NOT established.</t>
+  </si>
+  <si>
+    <t>NOAA OSPO satellite messages</t>
+  </si>
+  <si>
+    <t>2026-09-22T11:58:00Z</t>
+  </si>
+  <si>
+    <t>Product Anomaly/Outage: GOES-18/19 Product Distribution Outage, Issued: September 22, 2026 1158Z</t>
+  </si>
+  <si>
     <t>2026-09-21T04:50:00Z</t>
   </si>
   <si>
     <t>GOES-19</t>
   </si>
   <si>
-    <t>product/data</t>
-  </si>
-  <si>
-    <t>anomaly/outage</t>
-  </si>
-  <si>
-    <t>PRODUCT_DATA</t>
-  </si>
-  <si>
-    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
-  </si>
-  <si>
     <t>Product Anomaly/Outage: GOES-19 Aerosol, Cloud, and Land Meso-2 products-Issued: September 21, 2026 0450Z</t>
   </si>
   <si>
-    <t>Temporal association only; causality NOT established.</t>
-  </si>
-  <si>
-    <t>NOAA OSPO satellite messages</t>
-  </si>
-  <si>
     <t>2026-09-14T14:25:00Z</t>
   </si>
   <si>
@@ -182,9 +197,6 @@
     <t>2026-09-05T20:54:00Z</t>
   </si>
   <si>
-    <t>GOES-18</t>
-  </si>
-  <si>
     <t>Product Anomaly/Outage: Update #1: GOES-18, 19 - All Products products delivered to GRB - Issued: September 05, 2026 2054Z</t>
   </si>
   <si>
@@ -279,6 +291,9 @@
   </si>
   <si>
     <t>2026-09-22T10:20:32.345810Z</t>
+  </si>
+  <si>
+    <t>2026-09-22T15:11:28.994164Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1001,7 +1016,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1165,50 +1180,48 @@
       <c r="G4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4"/>
+      <c r="I4" s="6">
+        <v>2.61</v>
+      </c>
+      <c r="J4" s="6">
+        <v>324.33</v>
+      </c>
+      <c r="K4" s="6">
+        <v>556.4954833984375</v>
+      </c>
+      <c r="L4" s="6">
+        <v>15.68056297302246</v>
+      </c>
+      <c r="M4" s="6">
         <v>0.33</v>
       </c>
-      <c r="I4" s="6">
-        <v>-0.66</v>
-      </c>
-      <c r="J4" s="6">
-        <v>354.3</v>
-      </c>
-      <c r="K4" s="6">
-        <v>287.3075561523438</v>
-      </c>
-      <c r="L4" s="6">
-        <v>0.6605671048164368</v>
-      </c>
-      <c r="M4" s="6">
-        <v>1.67</v>
-      </c>
       <c r="N4" s="6">
-        <v>-2.11</v>
+        <v>-1.49</v>
       </c>
       <c r="O4" s="6">
-        <v>594.5599999999999</v>
+        <v>576.91</v>
       </c>
       <c r="P4" s="6">
         <v>2</v>
       </c>
       <c r="Q4" s="6">
-        <v>-4.05</v>
+        <v>-3.97</v>
       </c>
       <c r="R4" s="6">
-        <v>594.5599999999999</v>
+        <v>576.91</v>
       </c>
       <c r="S4" s="6">
         <v>3</v>
       </c>
       <c r="T4" s="6">
-        <v>-5.71</v>
+        <v>-4.14</v>
       </c>
       <c r="U4" s="6">
         <v>594.5599999999999</v>
       </c>
       <c r="V4" s="6">
-        <v>39.8</v>
+        <v>34.3</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>33</v>
@@ -1222,7 +1235,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>28</v>
@@ -1237,32 +1250,52 @@
         <v>31</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H5" s="6">
-        <v>4</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
+        <v>0.33</v>
+      </c>
+      <c r="I5" s="6">
+        <v>0.64</v>
+      </c>
+      <c r="J5" s="6">
+        <v>309.52</v>
+      </c>
+      <c r="K5" s="6">
+        <v>122.2937545776367</v>
+      </c>
+      <c r="L5" s="6">
+        <v>0.5407330989837646</v>
+      </c>
       <c r="M5" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
+        <v>0.33</v>
+      </c>
+      <c r="N5" s="6">
+        <v>-1.49</v>
+      </c>
+      <c r="O5" s="6">
+        <v>576.91</v>
+      </c>
       <c r="P5" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q5" s="6">
+        <v>-3.97</v>
+      </c>
+      <c r="R5" s="6">
+        <v>576.91</v>
+      </c>
       <c r="S5" s="6">
         <v>3</v>
       </c>
-      <c r="T5" s="4"/>
-      <c r="U5" s="4"/>
+      <c r="T5" s="6">
+        <v>-4.15</v>
+      </c>
+      <c r="U5" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="V5" s="6">
-        <v>5.8</v>
+        <v>34.3</v>
       </c>
       <c r="W5" s="4" t="s">
         <v>33</v>
@@ -1273,10 +1306,10 @@
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -1294,29 +1327,49 @@
         <v>39</v>
       </c>
       <c r="H6" s="6">
-        <v>4</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
+        <v>0.33</v>
+      </c>
+      <c r="I6" s="6">
+        <v>-0.66</v>
+      </c>
+      <c r="J6" s="6">
+        <v>354.3</v>
+      </c>
+      <c r="K6" s="6">
+        <v>287.3075561523438</v>
+      </c>
+      <c r="L6" s="6">
+        <v>0.6605671048164368</v>
+      </c>
       <c r="M6" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
+        <v>1.67</v>
+      </c>
+      <c r="N6" s="6">
+        <v>-2.11</v>
+      </c>
+      <c r="O6" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="P6" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-4.05</v>
+      </c>
+      <c r="R6" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="S6" s="6">
         <v>3</v>
       </c>
-      <c r="T6" s="4"/>
-      <c r="U6" s="4"/>
+      <c r="T6" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="U6" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="V6" s="6">
-        <v>5.8</v>
+        <v>39.8</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>33</v>
@@ -1330,7 +1383,7 @@
         <v>40</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>28</v>
@@ -1345,7 +1398,7 @@
         <v>31</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H7" s="6">
         <v>4</v>
@@ -1381,10 +1434,10 @@
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>28</v>
@@ -1399,7 +1452,7 @@
         <v>31</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H8" s="6">
         <v>4</v>
@@ -1435,50 +1488,50 @@
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>46</v>
+      <c r="E9" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H9" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="6">
-        <v>4.67</v>
+        <v>2.67</v>
       </c>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
       <c r="P9" s="6">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
       <c r="S9" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T9" s="4"/>
       <c r="U9" s="4"/>
       <c r="V9" s="6">
-        <v>17.5</v>
+        <v>5.8</v>
       </c>
       <c r="W9" s="4" t="s">
         <v>33</v>
@@ -1489,50 +1542,50 @@
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D10" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>46</v>
+      <c r="E10" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H10" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I10" s="4"/>
       <c r="J10" s="4"/>
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
       <c r="M10" s="6">
-        <v>4.67</v>
+        <v>2.67</v>
       </c>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
       <c r="P10" s="6">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
       <c r="S10" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T10" s="4"/>
       <c r="U10" s="4"/>
       <c r="V10" s="6">
-        <v>17.5</v>
+        <v>5.8</v>
       </c>
       <c r="W10" s="4" t="s">
         <v>33</v>
@@ -1543,28 +1596,28 @@
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>45</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H11" s="6">
-        <v>4.67</v>
+        <v>3</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
@@ -1597,19 +1650,19 @@
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>30</v>
+      <c r="E12" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>31</v>
@@ -1618,29 +1671,29 @@
         <v>54</v>
       </c>
       <c r="H12" s="6">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="6">
-        <v>0.33</v>
+        <v>4.67</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
       <c r="V12" s="6">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="W12" s="4" t="s">
         <v>33</v>
@@ -1654,16 +1707,16 @@
         <v>55</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>30</v>
+      <c r="E13" s="7" t="s">
+        <v>51</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>31</v>
@@ -1672,29 +1725,29 @@
         <v>56</v>
       </c>
       <c r="H13" s="6">
-        <v>0.33</v>
+        <v>4.67</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
       <c r="M13" s="6">
-        <v>0.33</v>
+        <v>4.67</v>
       </c>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
       <c r="P13" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="Q13" s="4"/>
       <c r="R13" s="4"/>
       <c r="S13" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="T13" s="4"/>
       <c r="U13" s="4"/>
       <c r="V13" s="6">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="W13" s="4" t="s">
         <v>33</v>
@@ -1708,7 +1761,7 @@
         <v>57</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C14" s="4" t="s">
         <v>28</v>
@@ -1726,19 +1779,19 @@
         <v>58</v>
       </c>
       <c r="H14" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="6">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="6">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
@@ -1762,7 +1815,7 @@
         <v>59</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>28</v>
@@ -1780,19 +1833,19 @@
         <v>60</v>
       </c>
       <c r="H15" s="6">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="6">
-        <v>1.67</v>
+        <v>0.33</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="6">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
@@ -1819,13 +1872,13 @@
         <v>27</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>46</v>
+      <c r="E16" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>31</v>
@@ -1834,14 +1887,14 @@
         <v>62</v>
       </c>
       <c r="H16" s="6">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="6">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
@@ -1865,8 +1918,116 @@
         <v>34</v>
       </c>
     </row>
+    <row r="17" spans="1:24">
+      <c r="A17" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="H17" s="6">
+        <v>2</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
+      <c r="M17" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="W17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X17" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24">
+      <c r="A18" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H18" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
+      <c r="M18" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="N18" s="4"/>
+      <c r="O18" s="4"/>
+      <c r="P18" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="Q18" s="4"/>
+      <c r="R18" s="4"/>
+      <c r="S18" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4"/>
+      <c r="V18" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="W18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X18" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:X16"/>
+  <autoFilter ref="A3:X18"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A2:X2"/>
@@ -1877,7 +2038,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -1886,7 +2047,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1899,36 +2060,36 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -1951,7 +2112,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B4" s="6">
         <v>0.67</v>
@@ -1980,7 +2141,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2003,7 +2164,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B6" s="6">
         <v>0.33</v>
@@ -2032,7 +2193,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2055,7 +2216,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="6">
@@ -2082,7 +2243,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B9" s="6">
         <v>1.67</v>
@@ -2111,7 +2272,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2134,7 +2295,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2157,7 +2318,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="6">
@@ -2184,7 +2345,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B13" s="6">
         <v>1.33</v>
@@ -2213,7 +2374,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B14" s="6">
         <v>2</v>
@@ -2242,7 +2403,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2263,8 +2424,35 @@
         <v>387.31</v>
       </c>
     </row>
+    <row r="16" spans="1:9">
+      <c r="A16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="6">
+        <v>-1.67</v>
+      </c>
+      <c r="D16" s="6">
+        <v>309.4</v>
+      </c>
+      <c r="E16" s="6">
+        <v>556.4954833984375</v>
+      </c>
+      <c r="F16" s="6">
+        <v>15.68056297302246</v>
+      </c>
+      <c r="G16" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H16" s="6">
+        <v>-8.51</v>
+      </c>
+      <c r="I16" s="6">
+        <v>396.99</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I15"/>
+  <autoFilter ref="A2:I16"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2286,7 +2474,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2301,39 +2489,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2359,17 +2547,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2377,145 +2565,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2523,56 +2711,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -13,15 +13,15 @@
     <sheet name="Method_Legend" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="158">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -101,33 +101,39 @@
     <t>Source</t>
   </si>
   <si>
+    <t>2026-09-22T16:35:00Z</t>
+  </si>
+  <si>
+    <t>GOES-18</t>
+  </si>
+  <si>
+    <t>product/data</t>
+  </si>
+  <si>
+    <t>anomaly/outage</t>
+  </si>
+  <si>
+    <t>PRODUCT_DATA</t>
+  </si>
+  <si>
+    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
+  </si>
+  <si>
+    <t>Product Anomaly/Outage: Update #2 - GOES-18/19 Product Distribution Outage, Issued: September 22, 2026 1635 UTC</t>
+  </si>
+  <si>
+    <t>Temporal association only; causality NOT established.</t>
+  </si>
+  <si>
+    <t>NOAA OSPO satellite messages</t>
+  </si>
+  <si>
     <t>2026-09-22T14:15:00Z</t>
   </si>
   <si>
-    <t>GOES-18</t>
-  </si>
-  <si>
-    <t>product/data</t>
-  </si>
-  <si>
-    <t>anomaly/outage</t>
-  </si>
-  <si>
-    <t>PRODUCT_DATA</t>
-  </si>
-  <si>
-    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
-  </si>
-  <si>
     <t>Product Anomaly/Outage: Update #1 - GOES-18/19 Product Distribution Outage, Issued: September 22, 2026 1415 UTC</t>
   </si>
   <si>
-    <t>Temporal association only; causality NOT established.</t>
-  </si>
-  <si>
-    <t>NOAA OSPO satellite messages</t>
-  </si>
-  <si>
     <t>2026-09-22T11:58:00Z</t>
   </si>
   <si>
@@ -294,6 +300,9 @@
   </si>
   <si>
     <t>2026-09-22T15:11:28.994164Z</t>
+  </si>
+  <si>
+    <t>2026-09-22T19:11:56.070370Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1016,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X18"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1180,12 +1189,14 @@
       <c r="G4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H4" s="4"/>
+      <c r="H4" s="6">
+        <v>0.67</v>
+      </c>
       <c r="I4" s="6">
-        <v>2.61</v>
+        <v>1.77</v>
       </c>
       <c r="J4" s="6">
-        <v>324.33</v>
+        <v>294</v>
       </c>
       <c r="K4" s="6">
         <v>556.4954833984375</v>
@@ -1194,19 +1205,19 @@
         <v>15.68056297302246</v>
       </c>
       <c r="M4" s="6">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="N4" s="6">
-        <v>-1.49</v>
+        <v>-3.02</v>
       </c>
       <c r="O4" s="6">
-        <v>576.91</v>
+        <v>476.79</v>
       </c>
       <c r="P4" s="6">
         <v>2</v>
       </c>
       <c r="Q4" s="6">
-        <v>-3.97</v>
+        <v>-3.92</v>
       </c>
       <c r="R4" s="6">
         <v>576.91</v>
@@ -1253,19 +1264,19 @@
         <v>36</v>
       </c>
       <c r="H5" s="6">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="I5" s="6">
-        <v>0.64</v>
+        <v>2.61</v>
       </c>
       <c r="J5" s="6">
-        <v>309.52</v>
+        <v>324.33</v>
       </c>
       <c r="K5" s="6">
-        <v>122.2937545776367</v>
+        <v>556.4954833984375</v>
       </c>
       <c r="L5" s="6">
-        <v>0.5407330989837646</v>
+        <v>15.68056297302246</v>
       </c>
       <c r="M5" s="6">
         <v>0.33</v>
@@ -1280,7 +1291,7 @@
         <v>2</v>
       </c>
       <c r="Q5" s="6">
-        <v>-3.97</v>
+        <v>-3.92</v>
       </c>
       <c r="R5" s="6">
         <v>576.91</v>
@@ -1289,7 +1300,7 @@
         <v>3</v>
       </c>
       <c r="T5" s="6">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="U5" s="6">
         <v>594.5599999999999</v>
@@ -1309,7 +1320,7 @@
         <v>37</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -1324,52 +1335,52 @@
         <v>31</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H6" s="6">
         <v>0.33</v>
       </c>
       <c r="I6" s="6">
-        <v>-0.66</v>
+        <v>0.64</v>
       </c>
       <c r="J6" s="6">
-        <v>354.3</v>
+        <v>309.52</v>
       </c>
       <c r="K6" s="6">
-        <v>287.3075561523438</v>
+        <v>122.2937545776367</v>
       </c>
       <c r="L6" s="6">
-        <v>0.6605671048164368</v>
+        <v>0.5407330989837646</v>
       </c>
       <c r="M6" s="6">
-        <v>1.67</v>
+        <v>0.33</v>
       </c>
       <c r="N6" s="6">
-        <v>-2.11</v>
+        <v>-1.49</v>
       </c>
       <c r="O6" s="6">
-        <v>594.5599999999999</v>
+        <v>576.91</v>
       </c>
       <c r="P6" s="6">
         <v>2</v>
       </c>
       <c r="Q6" s="6">
-        <v>-4.05</v>
+        <v>-3.92</v>
       </c>
       <c r="R6" s="6">
-        <v>594.5599999999999</v>
+        <v>576.91</v>
       </c>
       <c r="S6" s="6">
         <v>3</v>
       </c>
       <c r="T6" s="6">
-        <v>-5.71</v>
+        <v>-4.15</v>
       </c>
       <c r="U6" s="6">
         <v>594.5599999999999</v>
       </c>
       <c r="V6" s="6">
-        <v>39.8</v>
+        <v>34.3</v>
       </c>
       <c r="W6" s="4" t="s">
         <v>33</v>
@@ -1380,10 +1391,10 @@
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>40</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>28</v>
@@ -1398,32 +1409,52 @@
         <v>31</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H7" s="6">
-        <v>4</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
+        <v>0.33</v>
+      </c>
+      <c r="I7" s="6">
+        <v>-0.66</v>
+      </c>
+      <c r="J7" s="6">
+        <v>354.3</v>
+      </c>
+      <c r="K7" s="6">
+        <v>287.3075561523438</v>
+      </c>
+      <c r="L7" s="6">
+        <v>0.6605671048164368</v>
+      </c>
       <c r="M7" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
+        <v>1.67</v>
+      </c>
+      <c r="N7" s="6">
+        <v>-2.11</v>
+      </c>
+      <c r="O7" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="P7" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q7" s="6">
+        <v>-4.05</v>
+      </c>
+      <c r="R7" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="S7" s="6">
         <v>3</v>
       </c>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
+      <c r="T7" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="U7" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="V7" s="6">
-        <v>5.8</v>
+        <v>39.8</v>
       </c>
       <c r="W7" s="4" t="s">
         <v>33</v>
@@ -1434,10 +1465,10 @@
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
         <v>28</v>
@@ -1491,7 +1522,7 @@
         <v>45</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>28</v>
@@ -1545,7 +1576,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>28</v>
@@ -1599,47 +1630,47 @@
         <v>49</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>51</v>
+      <c r="E11" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H11" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I11" s="4"/>
       <c r="J11" s="4"/>
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
       <c r="M11" s="6">
-        <v>4.67</v>
+        <v>2.67</v>
       </c>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
       <c r="P11" s="6">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="Q11" s="4"/>
       <c r="R11" s="4"/>
       <c r="S11" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" s="4"/>
       <c r="U11" s="4"/>
       <c r="V11" s="6">
-        <v>17.5</v>
+        <v>5.8</v>
       </c>
       <c r="W11" s="4" t="s">
         <v>33</v>
@@ -1650,19 +1681,19 @@
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>31</v>
@@ -1707,16 +1738,16 @@
         <v>55</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>31</v>
@@ -1725,7 +1756,7 @@
         <v>56</v>
       </c>
       <c r="H13" s="6">
-        <v>4.67</v>
+        <v>3</v>
       </c>
       <c r="I13" s="4"/>
       <c r="J13" s="4"/>
@@ -1761,16 +1792,16 @@
         <v>57</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>30</v>
+      <c r="E14" s="7" t="s">
+        <v>53</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>31</v>
@@ -1779,29 +1810,29 @@
         <v>58</v>
       </c>
       <c r="H14" s="6">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="4"/>
       <c r="L14" s="4"/>
       <c r="M14" s="6">
-        <v>0.33</v>
+        <v>4.67</v>
       </c>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
       <c r="P14" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="Q14" s="4"/>
       <c r="R14" s="4"/>
       <c r="S14" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="T14" s="4"/>
       <c r="U14" s="4"/>
       <c r="V14" s="6">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="W14" s="4" t="s">
         <v>33</v>
@@ -1833,7 +1864,7 @@
         <v>60</v>
       </c>
       <c r="H15" s="6">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
@@ -1887,19 +1918,19 @@
         <v>62</v>
       </c>
       <c r="H16" s="6">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
       <c r="K16" s="4"/>
       <c r="L16" s="4"/>
       <c r="M16" s="6">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
       <c r="P16" s="6">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="Q16" s="4"/>
       <c r="R16" s="4"/>
@@ -1948,7 +1979,7 @@
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="6">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
@@ -1977,16 +2008,16 @@
         <v>65</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E18" s="7" t="s">
-        <v>51</v>
+      <c r="E18" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>31</v>
@@ -1995,7 +2026,7 @@
         <v>66</v>
       </c>
       <c r="H18" s="6">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="I18" s="4"/>
       <c r="J18" s="4"/>
@@ -2026,8 +2057,62 @@
         <v>34</v>
       </c>
     </row>
+    <row r="19" spans="1:24">
+      <c r="A19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
+      <c r="M19" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="N19" s="4"/>
+      <c r="O19" s="4"/>
+      <c r="P19" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="Q19" s="4"/>
+      <c r="R19" s="4"/>
+      <c r="S19" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4"/>
+      <c r="V19" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="W19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X19" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:X18"/>
+  <autoFilter ref="A3:X19"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A2:X2"/>
@@ -2038,7 +2123,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2047,7 +2132,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2060,36 +2145,36 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2112,7 +2197,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B4" s="6">
         <v>0.67</v>
@@ -2141,7 +2226,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2164,7 +2249,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B6" s="6">
         <v>0.33</v>
@@ -2193,7 +2278,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2216,7 +2301,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="6">
@@ -2243,7 +2328,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" s="6">
         <v>1.67</v>
@@ -2272,7 +2357,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2295,7 +2380,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2318,7 +2403,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="6">
@@ -2345,7 +2430,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B13" s="6">
         <v>1.33</v>
@@ -2374,7 +2459,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B14" s="6">
         <v>2</v>
@@ -2403,7 +2488,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2426,7 +2511,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="6">
@@ -2451,8 +2536,37 @@
         <v>396.99</v>
       </c>
     </row>
+    <row r="17" spans="1:9">
+      <c r="A17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B17" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="C17" s="6">
+        <v>2.06</v>
+      </c>
+      <c r="D17" s="6">
+        <v>293.7</v>
+      </c>
+      <c r="E17" s="6">
+        <v>414.4813232421875</v>
+      </c>
+      <c r="F17" s="6">
+        <v>9.832888603210449</v>
+      </c>
+      <c r="G17" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H17" s="6">
+        <v>-8.92</v>
+      </c>
+      <c r="I17" s="6">
+        <v>390.07</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I16"/>
+  <autoFilter ref="A2:I17"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2474,7 +2588,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2489,39 +2603,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2547,17 +2661,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2565,145 +2679,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2711,56 +2825,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="280" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="159">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -303,6 +303,9 @@
   </si>
   <si>
     <t>2026-09-22T19:11:56.070370Z</t>
+  </si>
+  <si>
+    <t>2026-09-22T22:29:52.804561Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2123,7 +2126,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2565,8 +2568,31 @@
         <v>390.07</v>
       </c>
     </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="6">
+        <v>392.4940490722656</v>
+      </c>
+      <c r="F18" s="6">
+        <v>9.99064826965332</v>
+      </c>
+      <c r="G18" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H18" s="6">
+        <v>-8.92</v>
+      </c>
+      <c r="I18" s="6">
+        <v>390.07</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I17"/>
+  <autoFilter ref="A2:I18"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2588,7 +2614,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2603,39 +2629,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2661,17 +2687,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2679,134 +2705,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2814,10 +2840,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2825,56 +2851,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="160">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -306,6 +306,9 @@
   </si>
   <si>
     <t>2026-09-22T22:29:52.804561Z</t>
+  </si>
+  <si>
+    <t>2026-09-23T00:56:15.973565Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1223,7 +1226,7 @@
         <v>-3.92</v>
       </c>
       <c r="R4" s="6">
-        <v>576.91</v>
+        <v>476.79</v>
       </c>
       <c r="S4" s="6">
         <v>3</v>
@@ -1285,10 +1288,10 @@
         <v>0.33</v>
       </c>
       <c r="N5" s="6">
-        <v>-1.49</v>
+        <v>-1.77</v>
       </c>
       <c r="O5" s="6">
-        <v>576.91</v>
+        <v>476.79</v>
       </c>
       <c r="P5" s="6">
         <v>2</v>
@@ -1297,7 +1300,7 @@
         <v>-3.92</v>
       </c>
       <c r="R5" s="6">
-        <v>576.91</v>
+        <v>476.79</v>
       </c>
       <c r="S5" s="6">
         <v>3</v>
@@ -1359,10 +1362,10 @@
         <v>0.33</v>
       </c>
       <c r="N6" s="6">
-        <v>-1.49</v>
+        <v>-1.77</v>
       </c>
       <c r="O6" s="6">
-        <v>576.91</v>
+        <v>476.79</v>
       </c>
       <c r="P6" s="6">
         <v>2</v>
@@ -1371,7 +1374,7 @@
         <v>-3.92</v>
       </c>
       <c r="R6" s="6">
-        <v>576.91</v>
+        <v>476.79</v>
       </c>
       <c r="S6" s="6">
         <v>3</v>
@@ -2126,7 +2129,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2591,8 +2594,35 @@
         <v>390.07</v>
       </c>
     </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="4"/>
+      <c r="C19" s="6">
+        <v>-1.77</v>
+      </c>
+      <c r="D19" s="6">
+        <v>290.51</v>
+      </c>
+      <c r="E19" s="6">
+        <v>219.9218139648438</v>
+      </c>
+      <c r="F19" s="6">
+        <v>5.697070121765137</v>
+      </c>
+      <c r="G19" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H19" s="6">
+        <v>-8.4</v>
+      </c>
+      <c r="I19" s="6">
+        <v>369.45</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I18"/>
+  <autoFilter ref="A2:I19"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2614,7 +2644,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2629,39 +2659,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2687,17 +2717,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2705,134 +2735,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>116</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2840,10 +2870,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2851,56 +2881,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="161">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -309,6 +309,9 @@
   </si>
   <si>
     <t>2026-09-23T00:56:15.973565Z</t>
+  </si>
+  <si>
+    <t>2026-09-23T06:39:54.391270Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1199,7 +1202,7 @@
         <v>0.67</v>
       </c>
       <c r="I4" s="6">
-        <v>1.77</v>
+        <v>0.12</v>
       </c>
       <c r="J4" s="6">
         <v>294</v>
@@ -1226,7 +1229,7 @@
         <v>-3.92</v>
       </c>
       <c r="R4" s="6">
-        <v>476.79</v>
+        <v>498.44</v>
       </c>
       <c r="S4" s="6">
         <v>3</v>
@@ -1300,7 +1303,7 @@
         <v>-3.92</v>
       </c>
       <c r="R5" s="6">
-        <v>476.79</v>
+        <v>498.44</v>
       </c>
       <c r="S5" s="6">
         <v>3</v>
@@ -1374,7 +1377,7 @@
         <v>-3.92</v>
       </c>
       <c r="R6" s="6">
-        <v>476.79</v>
+        <v>498.44</v>
       </c>
       <c r="S6" s="6">
         <v>3</v>
@@ -2129,7 +2132,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2621,8 +2624,35 @@
         <v>369.45</v>
       </c>
     </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" s="4"/>
+      <c r="C20" s="6">
+        <v>1.32</v>
+      </c>
+      <c r="D20" s="6">
+        <v>285.69</v>
+      </c>
+      <c r="E20" s="6">
+        <v>248.6818084716797</v>
+      </c>
+      <c r="F20" s="6">
+        <v>0.7719442248344421</v>
+      </c>
+      <c r="G20" s="6">
+        <v>1</v>
+      </c>
+      <c r="H20" s="6">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="I20" s="6">
+        <v>391.03</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I19"/>
+  <autoFilter ref="A2:I20"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2644,7 +2674,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2659,39 +2689,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2717,17 +2747,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2735,134 +2765,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2870,10 +2900,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2881,56 +2911,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="162">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -312,6 +312,9 @@
   </si>
   <si>
     <t>2026-09-23T06:39:54.391270Z</t>
+  </si>
+  <si>
+    <t>2026-09-23T12:08:42.503690Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1202,7 +1205,7 @@
         <v>0.67</v>
       </c>
       <c r="I4" s="6">
-        <v>0.12</v>
+        <v>1.77</v>
       </c>
       <c r="J4" s="6">
         <v>294</v>
@@ -2132,7 +2135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I20"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2651,8 +2654,35 @@
         <v>391.03</v>
       </c>
     </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" s="4"/>
+      <c r="C21" s="6">
+        <v>0.16</v>
+      </c>
+      <c r="D21" s="6">
+        <v>286.6</v>
+      </c>
+      <c r="E21" s="6">
+        <v>447.3298034667969</v>
+      </c>
+      <c r="F21" s="6">
+        <v>0.5703853964805603</v>
+      </c>
+      <c r="G21" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="H21" s="6">
+        <v>-6.67</v>
+      </c>
+      <c r="I21" s="6">
+        <v>379.55</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I20"/>
+  <autoFilter ref="A2:I21"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2674,7 +2704,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2689,39 +2719,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2747,17 +2777,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2765,134 +2795,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2900,10 +2930,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2911,56 +2941,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$22</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="163">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -315,6 +315,9 @@
   </si>
   <si>
     <t>2026-09-23T12:08:42.503690Z</t>
+  </si>
+  <si>
+    <t>2026-09-23T17:35:36.105347Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2135,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I21"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2681,8 +2684,37 @@
         <v>379.55</v>
       </c>
     </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="C22" s="6">
+        <v>9.18</v>
+      </c>
+      <c r="D22" s="6">
+        <v>302.74</v>
+      </c>
+      <c r="E22" s="6">
+        <v>984.0172119140625</v>
+      </c>
+      <c r="F22" s="6">
+        <v>26.44539833068848</v>
+      </c>
+      <c r="G22" s="6">
+        <v>1</v>
+      </c>
+      <c r="H22" s="6">
+        <v>-7.04</v>
+      </c>
+      <c r="I22" s="6">
+        <v>382.87</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I21"/>
+  <autoFilter ref="A2:I22"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2704,7 +2736,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2719,39 +2751,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2777,17 +2809,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2795,134 +2827,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2930,10 +2962,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2941,56 +2973,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="164">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -318,6 +318,9 @@
   </si>
   <si>
     <t>2026-09-23T17:35:36.105347Z</t>
+  </si>
+  <si>
+    <t>2026-09-23T20:41:34.348017Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2138,7 +2141,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:I23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2713,8 +2716,31 @@
         <v>382.87</v>
       </c>
     </row>
+    <row r="23" spans="1:9">
+      <c r="A23" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="6">
+        <v>285.6935424804688</v>
+      </c>
+      <c r="F23" s="6">
+        <v>140.1556243896484</v>
+      </c>
+      <c r="G23" s="6">
+        <v>1</v>
+      </c>
+      <c r="H23" s="6">
+        <v>-7.04</v>
+      </c>
+      <c r="I23" s="6">
+        <v>382.87</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I22"/>
+  <autoFilter ref="A2:I23"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2736,7 +2762,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2751,39 +2777,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2809,17 +2835,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2827,134 +2853,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>120</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2962,10 +2988,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2973,56 +2999,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="165">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -321,6 +321,9 @@
   </si>
   <si>
     <t>2026-09-23T20:41:34.348017Z</t>
+  </si>
+  <si>
+    <t>2026-09-23T23:10:37.504572Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2141,7 +2144,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I23"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2739,8 +2742,37 @@
         <v>382.87</v>
       </c>
     </row>
+    <row r="24" spans="1:9">
+      <c r="A24" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B24" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="C24" s="6">
+        <v>0.24</v>
+      </c>
+      <c r="D24" s="6">
+        <v>306.96</v>
+      </c>
+      <c r="E24" s="6">
+        <v>267.4169921875</v>
+      </c>
+      <c r="F24" s="6">
+        <v>27.41785430908203</v>
+      </c>
+      <c r="G24" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H24" s="6">
+        <v>-7.55</v>
+      </c>
+      <c r="I24" s="6">
+        <v>370.15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I23"/>
+  <autoFilter ref="A2:I24"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2762,7 +2794,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2777,39 +2809,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2835,17 +2867,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2853,134 +2885,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -2988,10 +3020,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2999,56 +3031,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="166">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -324,6 +324,9 @@
   </si>
   <si>
     <t>2026-09-23T23:10:37.504572Z</t>
+  </si>
+  <si>
+    <t>2026-09-24T01:39:36.808361Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2144,7 +2147,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2771,8 +2774,31 @@
         <v>370.15</v>
       </c>
     </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="6">
+        <v>275.0405578613281</v>
+      </c>
+      <c r="F25" s="6">
+        <v>10.27115345001221</v>
+      </c>
+      <c r="G25" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H25" s="6">
+        <v>-7.55</v>
+      </c>
+      <c r="I25" s="6">
+        <v>370.15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I24"/>
+  <autoFilter ref="A2:I25"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2794,7 +2820,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2809,39 +2835,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2867,17 +2893,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2885,134 +2911,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3020,10 +3046,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3031,56 +3057,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="167">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>2026-09-24T01:39:36.808361Z</t>
+  </si>
+  <si>
+    <t>2026-09-24T06:47:39.699027Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2147,7 +2150,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2797,8 +2800,35 @@
         <v>370.15</v>
       </c>
     </row>
+    <row r="26" spans="1:9">
+      <c r="A26" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B26" s="4"/>
+      <c r="C26" s="6">
+        <v>-4.28</v>
+      </c>
+      <c r="D26" s="6">
+        <v>324.47</v>
+      </c>
+      <c r="E26" s="6">
+        <v>25.82427787780762</v>
+      </c>
+      <c r="F26" s="6">
+        <v>0.3080306053161621</v>
+      </c>
+      <c r="G26" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="H26" s="6">
+        <v>-10.02</v>
+      </c>
+      <c r="I26" s="6">
+        <v>383.67</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I25"/>
+  <autoFilter ref="A2:I26"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2820,7 +2850,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2835,39 +2865,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2893,17 +2923,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2911,134 +2941,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>123</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3046,10 +3076,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3057,56 +3087,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$27</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="168">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -330,6 +330,9 @@
   </si>
   <si>
     <t>2026-09-24T06:47:39.699027Z</t>
+  </si>
+  <si>
+    <t>2026-09-24T12:54:37.051456Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2150,7 +2153,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2827,8 +2830,35 @@
         <v>383.67</v>
       </c>
     </row>
+    <row r="27" spans="1:9">
+      <c r="A27" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B27" s="4"/>
+      <c r="C27" s="6">
+        <v>-3.72</v>
+      </c>
+      <c r="D27" s="6">
+        <v>393.03</v>
+      </c>
+      <c r="E27" s="6">
+        <v>246.2023315429688</v>
+      </c>
+      <c r="F27" s="6">
+        <v>0.4561784565448761</v>
+      </c>
+      <c r="G27" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="H27" s="6">
+        <v>-15.29</v>
+      </c>
+      <c r="I27" s="6">
+        <v>388.28</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I26"/>
+  <autoFilter ref="A2:I27"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2850,7 +2880,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2865,39 +2895,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2923,17 +2953,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2941,134 +2971,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>124</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3076,10 +3106,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3087,56 +3117,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="169">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -333,6 +333,9 @@
   </si>
   <si>
     <t>2026-09-24T12:54:37.051456Z</t>
+  </si>
+  <si>
+    <t>2026-09-24T18:08:31.366820Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2153,7 +2156,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2857,8 +2860,35 @@
         <v>388.28</v>
       </c>
     </row>
+    <row r="28" spans="1:9">
+      <c r="A28" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" s="4"/>
+      <c r="C28" s="6">
+        <v>0.61</v>
+      </c>
+      <c r="D28" s="6">
+        <v>418.4</v>
+      </c>
+      <c r="E28" s="6">
+        <v>42.93707275390625</v>
+      </c>
+      <c r="F28" s="6">
+        <v>14.1708459854126</v>
+      </c>
+      <c r="G28" s="6">
+        <v>4</v>
+      </c>
+      <c r="H28" s="6">
+        <v>-7.32</v>
+      </c>
+      <c r="I28" s="6">
+        <v>384.69</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I27"/>
+  <autoFilter ref="A2:I28"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2880,7 +2910,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2895,39 +2925,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2953,17 +2983,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -2971,134 +3001,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>125</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3106,10 +3136,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3117,56 +3147,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="170">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -336,6 +336,9 @@
   </si>
   <si>
     <t>2026-09-24T18:08:31.366820Z</t>
+  </si>
+  <si>
+    <t>2026-09-25T00:49:00.691721Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2156,7 +2159,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2887,8 +2890,31 @@
         <v>384.69</v>
       </c>
     </row>
+    <row r="29" spans="1:9">
+      <c r="A29" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="6">
+        <v>167.166748046875</v>
+      </c>
+      <c r="F29" s="6">
+        <v>0.7954077124595642</v>
+      </c>
+      <c r="G29" s="6">
+        <v>2</v>
+      </c>
+      <c r="H29" s="6">
+        <v>-5.02</v>
+      </c>
+      <c r="I29" s="6">
+        <v>404.77</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I28"/>
+  <autoFilter ref="A2:I29"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2910,7 +2936,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2925,39 +2951,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -2983,17 +3009,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3001,134 +3027,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>126</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3136,10 +3162,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3147,56 +3173,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="171">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>2026-09-25T00:49:00.691721Z</t>
+  </si>
+  <si>
+    <t>2026-09-25T06:36:07.788058Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2159,7 +2162,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I29"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2913,8 +2916,35 @@
         <v>404.77</v>
       </c>
     </row>
+    <row r="30" spans="1:9">
+      <c r="A30" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="4"/>
+      <c r="C30" s="6">
+        <v>-6.37</v>
+      </c>
+      <c r="D30" s="6">
+        <v>477.74</v>
+      </c>
+      <c r="E30" s="6">
+        <v>6.08365535736084</v>
+      </c>
+      <c r="F30" s="6">
+        <v>2.145055770874023</v>
+      </c>
+      <c r="G30" s="6">
+        <v>3.67</v>
+      </c>
+      <c r="H30" s="6">
+        <v>-4.27</v>
+      </c>
+      <c r="I30" s="6">
+        <v>417.32</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I29"/>
+  <autoFilter ref="A2:I30"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2936,7 +2966,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2951,39 +2981,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3009,17 +3039,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3027,134 +3057,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3162,10 +3192,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3173,56 +3203,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="172">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -342,6 +342,9 @@
   </si>
   <si>
     <t>2026-09-25T06:36:07.788058Z</t>
+  </si>
+  <si>
+    <t>2026-09-25T12:12:51.093377Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2162,7 +2165,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2943,8 +2946,35 @@
         <v>417.32</v>
       </c>
     </row>
+    <row r="31" spans="1:9">
+      <c r="A31" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B31" s="4"/>
+      <c r="C31" s="6">
+        <v>-3.99</v>
+      </c>
+      <c r="D31" s="6">
+        <v>461.29</v>
+      </c>
+      <c r="E31" s="6">
+        <v>245.7528381347656</v>
+      </c>
+      <c r="F31" s="6">
+        <v>0.4111782014369965</v>
+      </c>
+      <c r="G31" s="6">
+        <v>4</v>
+      </c>
+      <c r="H31" s="6">
+        <v>-7.64</v>
+      </c>
+      <c r="I31" s="6">
+        <v>430.93</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I30"/>
+  <autoFilter ref="A2:I31"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2966,7 +2996,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2981,39 +3011,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3039,17 +3069,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3057,134 +3087,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>128</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3192,10 +3222,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3203,56 +3233,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$32</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="294" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="173">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -345,6 +345,9 @@
   </si>
   <si>
     <t>2026-09-25T12:12:51.093377Z</t>
+  </si>
+  <si>
+    <t>2026-09-25T17:33:04.903408Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2165,7 +2168,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2973,8 +2976,37 @@
         <v>430.93</v>
       </c>
     </row>
+    <row r="32" spans="1:9">
+      <c r="A32" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="B32" s="6">
+        <v>3.67</v>
+      </c>
+      <c r="C32" s="6">
+        <v>1.75</v>
+      </c>
+      <c r="D32" s="6">
+        <v>517.9</v>
+      </c>
+      <c r="E32" s="6">
+        <v>4</v>
+      </c>
+      <c r="F32" s="6">
+        <v>1.94412088394165</v>
+      </c>
+      <c r="G32" s="6">
+        <v>3.67</v>
+      </c>
+      <c r="H32" s="6">
+        <v>-6.46</v>
+      </c>
+      <c r="I32" s="6">
+        <v>430.36</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I31"/>
+  <autoFilter ref="A2:I32"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -2996,7 +3028,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3011,39 +3043,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3069,17 +3101,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3087,134 +3119,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3222,10 +3254,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3233,56 +3265,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$33</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="174">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -348,6 +348,9 @@
   </si>
   <si>
     <t>2026-09-25T17:33:04.903408Z</t>
+  </si>
+  <si>
+    <t>2026-09-25T20:45:45.891129Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2168,7 +2171,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3005,8 +3008,31 @@
         <v>430.36</v>
       </c>
     </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="B33" s="4"/>
+      <c r="C33" s="4"/>
+      <c r="D33" s="4"/>
+      <c r="E33" s="6">
+        <v>208.4181213378906</v>
+      </c>
+      <c r="F33" s="6">
+        <v>4.997064113616943</v>
+      </c>
+      <c r="G33" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="H33" s="6">
+        <v>-6.34</v>
+      </c>
+      <c r="I33" s="6">
+        <v>430.36</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I32"/>
+  <autoFilter ref="A2:I33"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3028,7 +3054,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3043,39 +3069,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3101,17 +3127,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3119,134 +3145,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3254,10 +3280,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3265,56 +3291,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="175">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>2026-09-25T20:45:45.891129Z</t>
+  </si>
+  <si>
+    <t>2026-09-26T00:10:25.885304Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2171,7 +2174,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:I34"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3031,8 +3034,31 @@
         <v>430.36</v>
       </c>
     </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B34" s="4"/>
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="6">
+        <v>204.216796875</v>
+      </c>
+      <c r="F34" s="6">
+        <v>1.863761901855469</v>
+      </c>
+      <c r="G34" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H34" s="6">
+        <v>-6.28</v>
+      </c>
+      <c r="I34" s="6">
+        <v>451.58</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I33"/>
+  <autoFilter ref="A2:I34"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3054,7 +3080,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3069,39 +3095,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3127,17 +3153,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3145,134 +3171,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3280,10 +3306,10 @@
         <v>53</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3291,56 +3317,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -13,15 +13,15 @@
     <sheet name="Method_Legend" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$19</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="178">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -101,33 +101,42 @@
     <t>Source</t>
   </si>
   <si>
+    <t>2026-09-26T01:03:00Z</t>
+  </si>
+  <si>
+    <t>GOES-18, GOES-19</t>
+  </si>
+  <si>
+    <t>product/data</t>
+  </si>
+  <si>
+    <t>anomaly/outage</t>
+  </si>
+  <si>
+    <t>PRODUCT_DATA</t>
+  </si>
+  <si>
+    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
+  </si>
+  <si>
+    <t>Product Outage/Anomaly: GOES-18, GOES-19 All Products and all scenes delivered to GRB - Issued September 26, 2026 0103Z</t>
+  </si>
+  <si>
+    <t>Temporal association only; causality NOT established.</t>
+  </si>
+  <si>
+    <t>NOAA OSPO satellite messages</t>
+  </si>
+  <si>
     <t>2026-09-22T16:35:00Z</t>
   </si>
   <si>
     <t>GOES-18</t>
   </si>
   <si>
-    <t>product/data</t>
-  </si>
-  <si>
-    <t>anomaly/outage</t>
-  </si>
-  <si>
-    <t>PRODUCT_DATA</t>
-  </si>
-  <si>
-    <t>CATEGORY_FROM_PUBLIC_TEXT_NOT_ROOT_CAUSE</t>
-  </si>
-  <si>
     <t>Product Anomaly/Outage: Update #2 - GOES-18/19 Product Distribution Outage, Issued: September 22, 2026 1635 UTC</t>
   </si>
   <si>
-    <t>Temporal association only; causality NOT established.</t>
-  </si>
-  <si>
-    <t>NOAA OSPO satellite messages</t>
-  </si>
-  <si>
     <t>2026-09-22T14:15:00Z</t>
   </si>
   <si>
@@ -152,9 +161,6 @@
     <t>2026-09-14T14:25:00Z</t>
   </si>
   <si>
-    <t>GOES-18, GOES-19</t>
-  </si>
-  <si>
     <t>Product Anomaly/Outage: Impact to GOES-18, GOES-19, and SOLAR-1 Products Issued: September 14, 2026 1425Z</t>
   </si>
   <si>
@@ -354,6 +360,9 @@
   </si>
   <si>
     <t>2026-09-26T00:10:25.885304Z</t>
+  </si>
+  <si>
+    <t>2026-09-26T05:28:11.849520Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1076,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X19"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" customWidth="1"/>
@@ -1241,49 +1250,49 @@
         <v>32</v>
       </c>
       <c r="H4" s="6">
-        <v>0.67</v>
+        <v>3.33</v>
       </c>
       <c r="I4" s="6">
-        <v>1.77</v>
+        <v>1.23</v>
       </c>
       <c r="J4" s="6">
-        <v>294</v>
+        <v>505.66</v>
       </c>
       <c r="K4" s="6">
-        <v>556.4954833984375</v>
+        <v>204.216796875</v>
       </c>
       <c r="L4" s="6">
-        <v>15.68056297302246</v>
+        <v>1.863761901855469</v>
       </c>
       <c r="M4" s="6">
-        <v>0.67</v>
+        <v>3.67</v>
       </c>
       <c r="N4" s="6">
-        <v>-3.02</v>
+        <v>-5.26</v>
       </c>
       <c r="O4" s="6">
-        <v>476.79</v>
+        <v>541.89</v>
       </c>
       <c r="P4" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q4" s="6">
-        <v>-3.92</v>
+        <v>-9.27</v>
       </c>
       <c r="R4" s="6">
-        <v>498.44</v>
+        <v>557.2</v>
       </c>
       <c r="S4" s="6">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="T4" s="6">
-        <v>-4.14</v>
+        <v>-12.98</v>
       </c>
       <c r="U4" s="6">
-        <v>594.5599999999999</v>
+        <v>557.2</v>
       </c>
       <c r="V4" s="6">
-        <v>34.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="W4" s="4" t="s">
         <v>33</v>
@@ -1297,7 +1306,7 @@
         <v>35</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>28</v>
@@ -1312,16 +1321,16 @@
         <v>31</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H5" s="6">
         <v>0.67</v>
       </c>
       <c r="I5" s="6">
-        <v>2.61</v>
+        <v>1.77</v>
       </c>
       <c r="J5" s="6">
-        <v>324.33</v>
+        <v>294</v>
       </c>
       <c r="K5" s="6">
         <v>556.4954833984375</v>
@@ -1330,10 +1339,10 @@
         <v>15.68056297302246</v>
       </c>
       <c r="M5" s="6">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="N5" s="6">
-        <v>-1.77</v>
+        <v>-3.02</v>
       </c>
       <c r="O5" s="6">
         <v>476.79</v>
@@ -1368,10 +1377,10 @@
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>28</v>
@@ -1386,22 +1395,22 @@
         <v>31</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H6" s="6">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="I6" s="6">
-        <v>0.64</v>
+        <v>2.61</v>
       </c>
       <c r="J6" s="6">
-        <v>309.52</v>
+        <v>324.33</v>
       </c>
       <c r="K6" s="6">
-        <v>122.2937545776367</v>
+        <v>556.4954833984375</v>
       </c>
       <c r="L6" s="6">
-        <v>0.5407330989837646</v>
+        <v>15.68056297302246</v>
       </c>
       <c r="M6" s="6">
         <v>0.33</v>
@@ -1425,7 +1434,7 @@
         <v>3</v>
       </c>
       <c r="T6" s="6">
-        <v>-4.15</v>
+        <v>-4.14</v>
       </c>
       <c r="U6" s="6">
         <v>594.5599999999999</v>
@@ -1442,10 +1451,10 @@
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>28</v>
@@ -1466,46 +1475,46 @@
         <v>0.33</v>
       </c>
       <c r="I7" s="6">
-        <v>-0.66</v>
+        <v>0.64</v>
       </c>
       <c r="J7" s="6">
-        <v>354.3</v>
+        <v>309.52</v>
       </c>
       <c r="K7" s="6">
-        <v>287.3075561523438</v>
+        <v>122.2937545776367</v>
       </c>
       <c r="L7" s="6">
-        <v>0.6605671048164368</v>
+        <v>0.5407330989837646</v>
       </c>
       <c r="M7" s="6">
-        <v>1.67</v>
+        <v>0.33</v>
       </c>
       <c r="N7" s="6">
-        <v>-2.11</v>
+        <v>-1.77</v>
       </c>
       <c r="O7" s="6">
-        <v>594.5599999999999</v>
+        <v>476.79</v>
       </c>
       <c r="P7" s="6">
         <v>2</v>
       </c>
       <c r="Q7" s="6">
-        <v>-4.05</v>
+        <v>-3.92</v>
       </c>
       <c r="R7" s="6">
-        <v>594.5599999999999</v>
+        <v>498.44</v>
       </c>
       <c r="S7" s="6">
         <v>3</v>
       </c>
       <c r="T7" s="6">
-        <v>-5.71</v>
+        <v>-4.15</v>
       </c>
       <c r="U7" s="6">
         <v>594.5599999999999</v>
       </c>
       <c r="V7" s="6">
-        <v>39.8</v>
+        <v>34.3</v>
       </c>
       <c r="W7" s="4" t="s">
         <v>33</v>
@@ -1537,29 +1546,49 @@
         <v>44</v>
       </c>
       <c r="H8" s="6">
-        <v>4</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
+        <v>0.33</v>
+      </c>
+      <c r="I8" s="6">
+        <v>-0.66</v>
+      </c>
+      <c r="J8" s="6">
+        <v>354.3</v>
+      </c>
+      <c r="K8" s="6">
+        <v>287.3075561523438</v>
+      </c>
+      <c r="L8" s="6">
+        <v>0.6605671048164368</v>
+      </c>
       <c r="M8" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="N8" s="4"/>
-      <c r="O8" s="4"/>
+        <v>1.67</v>
+      </c>
+      <c r="N8" s="6">
+        <v>-2.11</v>
+      </c>
+      <c r="O8" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="P8" s="6">
-        <v>2.67</v>
-      </c>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="Q8" s="6">
+        <v>-4.05</v>
+      </c>
+      <c r="R8" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="S8" s="6">
         <v>3</v>
       </c>
-      <c r="T8" s="4"/>
-      <c r="U8" s="4"/>
+      <c r="T8" s="6">
+        <v>-5.71</v>
+      </c>
+      <c r="U8" s="6">
+        <v>594.5599999999999</v>
+      </c>
       <c r="V8" s="6">
-        <v>5.8</v>
+        <v>39.8</v>
       </c>
       <c r="W8" s="4" t="s">
         <v>33</v>
@@ -1573,7 +1602,7 @@
         <v>45</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C9" s="4" t="s">
         <v>28</v>
@@ -1627,7 +1656,7 @@
         <v>47</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C10" s="4" t="s">
         <v>28</v>
@@ -1681,7 +1710,7 @@
         <v>49</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>28</v>
@@ -1735,47 +1764,47 @@
         <v>51</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="7" t="s">
-        <v>53</v>
+      <c r="E12" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>31</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H12" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I12" s="4"/>
       <c r="J12" s="4"/>
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
       <c r="M12" s="6">
-        <v>4.67</v>
+        <v>2.67</v>
       </c>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
       <c r="P12" s="6">
-        <v>5</v>
+        <v>2.67</v>
       </c>
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
       <c r="S12" s="6">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T12" s="4"/>
       <c r="U12" s="4"/>
       <c r="V12" s="6">
-        <v>17.5</v>
+        <v>5.8</v>
       </c>
       <c r="W12" s="4" t="s">
         <v>33</v>
@@ -1786,19 +1815,19 @@
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D13" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>31</v>
@@ -1843,16 +1872,16 @@
         <v>57</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>29</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>31</v>
@@ -1861,7 +1890,7 @@
         <v>58</v>
       </c>
       <c r="H14" s="6">
-        <v>4.67</v>
+        <v>3</v>
       </c>
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
@@ -1897,16 +1926,16 @@
         <v>59</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E15" s="5" t="s">
-        <v>30</v>
+      <c r="E15" s="7" t="s">
+        <v>55</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>31</v>
@@ -1915,29 +1944,29 @@
         <v>60</v>
       </c>
       <c r="H15" s="6">
-        <v>1</v>
+        <v>4.67</v>
       </c>
       <c r="I15" s="4"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
       <c r="L15" s="4"/>
       <c r="M15" s="6">
-        <v>0.33</v>
+        <v>4.67</v>
       </c>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
       <c r="P15" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
       <c r="S15" s="6">
-        <v>2.67</v>
+        <v>5</v>
       </c>
       <c r="T15" s="4"/>
       <c r="U15" s="4"/>
       <c r="V15" s="6">
-        <v>3.9</v>
+        <v>17.5</v>
       </c>
       <c r="W15" s="4" t="s">
         <v>33</v>
@@ -1951,7 +1980,7 @@
         <v>61</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>28</v>
@@ -1969,7 +1998,7 @@
         <v>62</v>
       </c>
       <c r="H16" s="6">
-        <v>0.33</v>
+        <v>1</v>
       </c>
       <c r="I16" s="4"/>
       <c r="J16" s="4"/>
@@ -2005,7 +2034,7 @@
         <v>63</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C17" s="4" t="s">
         <v>28</v>
@@ -2023,19 +2052,19 @@
         <v>64</v>
       </c>
       <c r="H17" s="6">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="I17" s="4"/>
       <c r="J17" s="4"/>
       <c r="K17" s="4"/>
       <c r="L17" s="4"/>
       <c r="M17" s="6">
-        <v>2</v>
+        <v>0.33</v>
       </c>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
       <c r="P17" s="6">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="Q17" s="4"/>
       <c r="R17" s="4"/>
@@ -2059,7 +2088,7 @@
         <v>65</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="C18" s="4" t="s">
         <v>28</v>
@@ -2084,7 +2113,7 @@
       <c r="K18" s="4"/>
       <c r="L18" s="4"/>
       <c r="M18" s="6">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
@@ -2113,16 +2142,16 @@
         <v>67</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>53</v>
+      <c r="E19" s="5" t="s">
+        <v>30</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>31</v>
@@ -2131,7 +2160,7 @@
         <v>68</v>
       </c>
       <c r="H19" s="6">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="I19" s="4"/>
       <c r="J19" s="4"/>
@@ -2162,8 +2191,62 @@
         <v>34</v>
       </c>
     </row>
+    <row r="20" spans="1:24">
+      <c r="A20" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
+      <c r="M20" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="N20" s="4"/>
+      <c r="O20" s="4"/>
+      <c r="P20" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="Q20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4"/>
+      <c r="V20" s="6">
+        <v>3.9</v>
+      </c>
+      <c r="W20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="X20" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A3:X19"/>
+  <autoFilter ref="A3:X20"/>
   <mergeCells count="2">
     <mergeCell ref="A1:X1"/>
     <mergeCell ref="A2:X2"/>
@@ -2174,7 +2257,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:I35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -2183,7 +2266,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2196,36 +2279,36 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2248,7 +2331,7 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="4" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B4" s="6">
         <v>0.67</v>
@@ -2277,7 +2360,7 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -2300,7 +2383,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B6" s="6">
         <v>0.33</v>
@@ -2329,7 +2412,7 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -2352,7 +2435,7 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B8" s="4"/>
       <c r="C8" s="6">
@@ -2379,7 +2462,7 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B9" s="6">
         <v>1.67</v>
@@ -2408,7 +2491,7 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="4" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
@@ -2431,7 +2514,7 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="4" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
@@ -2454,7 +2537,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="6">
@@ -2481,7 +2564,7 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B13" s="6">
         <v>1.33</v>
@@ -2510,7 +2593,7 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="4" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B14" s="6">
         <v>2</v>
@@ -2539,7 +2622,7 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -2562,7 +2645,7 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B16" s="4"/>
       <c r="C16" s="6">
@@ -2589,7 +2672,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="4" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B17" s="6">
         <v>0.67</v>
@@ -2618,7 +2701,7 @@
     </row>
     <row r="18" spans="1:9">
       <c r="A18" s="4" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
@@ -2641,7 +2724,7 @@
     </row>
     <row r="19" spans="1:9">
       <c r="A19" s="4" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B19" s="4"/>
       <c r="C19" s="6">
@@ -2668,7 +2751,7 @@
     </row>
     <row r="20" spans="1:9">
       <c r="A20" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B20" s="4"/>
       <c r="C20" s="6">
@@ -2695,7 +2778,7 @@
     </row>
     <row r="21" spans="1:9">
       <c r="A21" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B21" s="4"/>
       <c r="C21" s="6">
@@ -2722,7 +2805,7 @@
     </row>
     <row r="22" spans="1:9">
       <c r="A22" s="4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B22" s="6">
         <v>0.67</v>
@@ -2751,7 +2834,7 @@
     </row>
     <row r="23" spans="1:9">
       <c r="A23" s="4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -2774,7 +2857,7 @@
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B24" s="6">
         <v>1.67</v>
@@ -2803,7 +2886,7 @@
     </row>
     <row r="25" spans="1:9">
       <c r="A25" s="4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -2826,7 +2909,7 @@
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="4" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="6">
@@ -2853,7 +2936,7 @@
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="4" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B27" s="4"/>
       <c r="C27" s="6">
@@ -2880,7 +2963,7 @@
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B28" s="4"/>
       <c r="C28" s="6">
@@ -2907,7 +2990,7 @@
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -2930,7 +3013,7 @@
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B30" s="4"/>
       <c r="C30" s="6">
@@ -2957,7 +3040,7 @@
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B31" s="4"/>
       <c r="C31" s="6">
@@ -2984,7 +3067,7 @@
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="4" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B32" s="6">
         <v>3.67</v>
@@ -3013,7 +3096,7 @@
     </row>
     <row r="33" spans="1:9">
       <c r="A33" s="4" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -3036,7 +3119,7 @@
     </row>
     <row r="34" spans="1:9">
       <c r="A34" s="4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -3057,8 +3140,37 @@
         <v>451.58</v>
       </c>
     </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B35" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="C35" s="6">
+        <v>-2.38</v>
+      </c>
+      <c r="D35" s="6">
+        <v>468.05</v>
+      </c>
+      <c r="E35" s="6">
+        <v>251.6090240478516</v>
+      </c>
+      <c r="F35" s="6">
+        <v>0.7996945977210999</v>
+      </c>
+      <c r="G35" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="H35" s="6">
+        <v>-6.84</v>
+      </c>
+      <c r="I35" s="6">
+        <v>436.32</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I34"/>
+  <autoFilter ref="A2:I35"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3080,7 +3192,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3095,39 +3207,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3153,17 +3265,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3171,145 +3283,145 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3317,56 +3429,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="308" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="179">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>2026-09-26T05:28:11.849520Z</t>
+  </si>
+  <si>
+    <t>2026-09-26T10:15:35.223415Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2257,7 +2260,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3169,8 +3172,31 @@
         <v>436.32</v>
       </c>
     </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="4"/>
+      <c r="C36" s="4"/>
+      <c r="D36" s="4"/>
+      <c r="E36" s="6">
+        <v>229.4656372070312</v>
+      </c>
+      <c r="F36" s="6">
+        <v>0.2445084005594254</v>
+      </c>
+      <c r="G36" s="6">
+        <v>3.33</v>
+      </c>
+      <c r="H36" s="6">
+        <v>-6.84</v>
+      </c>
+      <c r="I36" s="6">
+        <v>436.32</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I35"/>
+  <autoFilter ref="A2:I36"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3192,7 +3218,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3207,39 +3233,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3265,17 +3291,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3283,134 +3309,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>135</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3418,10 +3444,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3429,56 +3455,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$37</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="180">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -366,6 +366,9 @@
   </si>
   <si>
     <t>2026-09-26T10:15:35.223415Z</t>
+  </si>
+  <si>
+    <t>2026-09-26T14:44:15.566858Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1256,7 +1259,7 @@
         <v>3.33</v>
       </c>
       <c r="I4" s="6">
-        <v>1.23</v>
+        <v>0.86</v>
       </c>
       <c r="J4" s="6">
         <v>505.66</v>
@@ -1271,7 +1274,7 @@
         <v>3.67</v>
       </c>
       <c r="N4" s="6">
-        <v>-5.26</v>
+        <v>-5.2</v>
       </c>
       <c r="O4" s="6">
         <v>541.89</v>
@@ -1283,7 +1286,7 @@
         <v>-9.27</v>
       </c>
       <c r="R4" s="6">
-        <v>557.2</v>
+        <v>557.66</v>
       </c>
       <c r="S4" s="6">
         <v>4.33</v>
@@ -1292,7 +1295,7 @@
         <v>-12.98</v>
       </c>
       <c r="U4" s="6">
-        <v>557.2</v>
+        <v>557.66</v>
       </c>
       <c r="V4" s="6">
         <v>66.40000000000001</v>
@@ -2260,7 +2263,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I36"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3195,8 +3198,31 @@
         <v>436.32</v>
       </c>
     </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="6">
+        <v>989.056884765625</v>
+      </c>
+      <c r="F37" s="6">
+        <v>5.483329772949219</v>
+      </c>
+      <c r="G37" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="H37" s="6">
+        <v>-7.24</v>
+      </c>
+      <c r="I37" s="6">
+        <v>426.83</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I36"/>
+  <autoFilter ref="A2:I37"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3218,7 +3244,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3233,39 +3259,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3291,17 +3317,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3309,134 +3335,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3444,10 +3470,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3455,56 +3481,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="181">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -369,6 +369,9 @@
   </si>
   <si>
     <t>2026-09-26T14:44:15.566858Z</t>
+  </si>
+  <si>
+    <t>2026-09-26T18:43:48.384455Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1259,7 +1262,7 @@
         <v>3.33</v>
       </c>
       <c r="I4" s="6">
-        <v>0.86</v>
+        <v>1.23</v>
       </c>
       <c r="J4" s="6">
         <v>505.66</v>
@@ -1274,10 +1277,10 @@
         <v>3.67</v>
       </c>
       <c r="N4" s="6">
-        <v>-5.2</v>
+        <v>-5.26</v>
       </c>
       <c r="O4" s="6">
-        <v>541.89</v>
+        <v>531.29</v>
       </c>
       <c r="P4" s="6">
         <v>4</v>
@@ -1286,7 +1289,7 @@
         <v>-9.27</v>
       </c>
       <c r="R4" s="6">
-        <v>557.66</v>
+        <v>557.2</v>
       </c>
       <c r="S4" s="6">
         <v>4.33</v>
@@ -1295,7 +1298,7 @@
         <v>-12.98</v>
       </c>
       <c r="U4" s="6">
-        <v>557.66</v>
+        <v>557.2</v>
       </c>
       <c r="V4" s="6">
         <v>66.40000000000001</v>
@@ -2263,7 +2266,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3221,8 +3224,31 @@
         <v>426.83</v>
       </c>
     </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="B38" s="4"/>
+      <c r="C38" s="4"/>
+      <c r="D38" s="4"/>
+      <c r="E38" s="6">
+        <v>1009.264099121094</v>
+      </c>
+      <c r="F38" s="6">
+        <v>10.29182815551758</v>
+      </c>
+      <c r="G38" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H38" s="6">
+        <v>-7.33</v>
+      </c>
+      <c r="I38" s="6">
+        <v>435.15</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I37"/>
+  <autoFilter ref="A2:I38"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3244,7 +3270,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3259,39 +3285,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3317,17 +3343,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3335,134 +3361,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>137</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3470,10 +3496,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3481,56 +3507,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="182">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -372,6 +372,9 @@
   </si>
   <si>
     <t>2026-09-26T18:43:48.384455Z</t>
+  </si>
+  <si>
+    <t>2026-09-26T21:36:45.770510Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1277,7 +1280,7 @@
         <v>3.67</v>
       </c>
       <c r="N4" s="6">
-        <v>-5.26</v>
+        <v>-5.14</v>
       </c>
       <c r="O4" s="6">
         <v>531.29</v>
@@ -2266,7 +2269,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3247,8 +3250,37 @@
         <v>435.15</v>
       </c>
     </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="C39" s="6">
+        <v>-2.3</v>
+      </c>
+      <c r="D39" s="6">
+        <v>463.99</v>
+      </c>
+      <c r="E39" s="6">
+        <v>160.1730194091797</v>
+      </c>
+      <c r="F39" s="6">
+        <v>6.205619335174561</v>
+      </c>
+      <c r="G39" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="H39" s="6">
+        <v>-6.87</v>
+      </c>
+      <c r="I39" s="6">
+        <v>432.96</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I38"/>
+  <autoFilter ref="A2:I39"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3270,7 +3302,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3285,39 +3317,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3343,17 +3375,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3361,134 +3393,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3496,10 +3528,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3507,56 +3539,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$40</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="183">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -375,6 +375,9 @@
   </si>
   <si>
     <t>2026-09-26T21:36:45.770510Z</t>
+  </si>
+  <si>
+    <t>2026-09-26T23:54:03.637299Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2269,7 +2272,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3279,8 +3282,33 @@
         <v>432.96</v>
       </c>
     </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" s="6">
+        <v>2.33</v>
+      </c>
+      <c r="C40" s="4"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="6">
+        <v>74.93085479736328</v>
+      </c>
+      <c r="F40" s="6">
+        <v>1.637504577636719</v>
+      </c>
+      <c r="G40" s="6">
+        <v>2.67</v>
+      </c>
+      <c r="H40" s="6">
+        <v>-6.87</v>
+      </c>
+      <c r="I40" s="6">
+        <v>424.75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I39"/>
+  <autoFilter ref="A2:I40"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3302,7 +3330,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3317,39 +3345,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3375,17 +3403,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3393,134 +3421,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>139</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3528,10 +3556,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3539,56 +3567,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$41</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="184">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -378,6 +378,9 @@
   </si>
   <si>
     <t>2026-09-26T23:54:03.637299Z</t>
+  </si>
+  <si>
+    <t>2026-09-27T05:45:01.917846Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -1268,10 +1271,10 @@
         <v>3.33</v>
       </c>
       <c r="I4" s="6">
-        <v>1.23</v>
+        <v>0.86</v>
       </c>
       <c r="J4" s="6">
-        <v>505.66</v>
+        <v>496.3</v>
       </c>
       <c r="K4" s="6">
         <v>204.216796875</v>
@@ -2272,7 +2275,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3307,8 +3310,37 @@
         <v>424.75</v>
       </c>
     </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B41" s="6">
+        <v>4</v>
+      </c>
+      <c r="C41" s="6">
+        <v>0.51</v>
+      </c>
+      <c r="D41" s="6">
+        <v>442.77</v>
+      </c>
+      <c r="E41" s="6">
+        <v>1060.859130859375</v>
+      </c>
+      <c r="F41" s="6">
+        <v>1.64462423324585</v>
+      </c>
+      <c r="G41" s="6">
+        <v>3.67</v>
+      </c>
+      <c r="H41" s="6">
+        <v>-5.57</v>
+      </c>
+      <c r="I41" s="6">
+        <v>414.99</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I40"/>
+  <autoFilter ref="A2:I41"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3330,7 +3362,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3345,39 +3377,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3403,17 +3435,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3421,134 +3453,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>140</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3556,10 +3588,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3567,56 +3599,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="185">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>2026-09-27T05:45:01.917846Z</t>
+  </si>
+  <si>
+    <t>2026-09-27T12:27:39.366784Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2275,7 +2278,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3339,8 +3342,37 @@
         <v>414.99</v>
       </c>
     </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B42" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-1.39</v>
+      </c>
+      <c r="D42" s="6">
+        <v>419.15</v>
+      </c>
+      <c r="E42" s="6">
+        <v>1259.86083984375</v>
+      </c>
+      <c r="F42" s="6">
+        <v>0.366377979516983</v>
+      </c>
+      <c r="G42" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H42" s="6">
+        <v>-5.55</v>
+      </c>
+      <c r="I42" s="6">
+        <v>415.37</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I41"/>
+  <autoFilter ref="A2:I42"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3362,7 +3394,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3377,39 +3409,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3435,17 +3467,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3453,134 +3485,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3588,10 +3620,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3599,56 +3631,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="186">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -384,6 +384,9 @@
   </si>
   <si>
     <t>2026-09-27T12:27:39.366784Z</t>
+  </si>
+  <si>
+    <t>2026-09-27T17:17:20.127642Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2278,7 +2281,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3371,8 +3374,37 @@
         <v>415.37</v>
       </c>
     </row>
+    <row r="43" spans="1:9">
+      <c r="A43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B43" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="C43" s="6">
+        <v>0.72</v>
+      </c>
+      <c r="D43" s="6">
+        <v>398.85</v>
+      </c>
+      <c r="E43" s="6">
+        <v>2799.478759765625</v>
+      </c>
+      <c r="F43" s="6">
+        <v>1.594094753265381</v>
+      </c>
+      <c r="G43" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H43" s="6">
+        <v>-5.33</v>
+      </c>
+      <c r="I43" s="6">
+        <v>422.42</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I42"/>
+  <autoFilter ref="A2:I43"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3394,7 +3426,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3409,39 +3441,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3467,17 +3499,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3485,134 +3517,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3620,10 +3652,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3631,56 +3663,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$44</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="187">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -387,6 +387,9 @@
   </si>
   <si>
     <t>2026-09-27T17:17:20.127642Z</t>
+  </si>
+  <si>
+    <t>2026-09-27T20:23:56.993848Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2281,7 +2284,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3403,8 +3406,31 @@
         <v>422.42</v>
       </c>
     </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="6">
+        <v>2121.389404296875</v>
+      </c>
+      <c r="F44" s="6">
+        <v>5.561851978302002</v>
+      </c>
+      <c r="G44" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H44" s="6">
+        <v>-5.4</v>
+      </c>
+      <c r="I44" s="6">
+        <v>495.58</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I43"/>
+  <autoFilter ref="A2:I44"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3426,7 +3452,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3441,39 +3467,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3499,17 +3525,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3517,134 +3543,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3652,10 +3678,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3663,56 +3689,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$44</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="188">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -390,6 +390,9 @@
   </si>
   <si>
     <t>2026-09-27T20:23:56.993848Z</t>
+  </si>
+  <si>
+    <t>2026-09-27T23:25:10.209304Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2284,7 +2287,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3429,8 +3432,33 @@
         <v>495.58</v>
       </c>
     </row>
+    <row r="45" spans="1:9">
+      <c r="A45" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B45" s="6">
+        <v>0.33</v>
+      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="4"/>
+      <c r="E45" s="6">
+        <v>1888.0634765625</v>
+      </c>
+      <c r="F45" s="6">
+        <v>6.339443683624268</v>
+      </c>
+      <c r="G45" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H45" s="6">
+        <v>-5.06</v>
+      </c>
+      <c r="I45" s="6">
+        <v>568.6900000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I44"/>
+  <autoFilter ref="A2:I45"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3452,7 +3480,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3467,39 +3495,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3525,17 +3553,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3543,134 +3571,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>144</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3678,10 +3706,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3689,56 +3717,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$46</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="189">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -393,6 +393,9 @@
   </si>
   <si>
     <t>2026-09-27T23:25:10.209304Z</t>
+  </si>
+  <si>
+    <t>2026-09-28T01:59:30.329228Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2287,7 +2290,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:I46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3457,8 +3460,31 @@
         <v>568.6900000000001</v>
       </c>
     </row>
+    <row r="46" spans="1:9">
+      <c r="A46" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B46" s="4"/>
+      <c r="C46" s="4"/>
+      <c r="D46" s="4"/>
+      <c r="E46" s="6">
+        <v>1393.084106445312</v>
+      </c>
+      <c r="F46" s="6">
+        <v>3.366036891937256</v>
+      </c>
+      <c r="G46" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H46" s="6">
+        <v>-5.1</v>
+      </c>
+      <c r="I46" s="6">
+        <v>587.1799999999999</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I45"/>
+  <autoFilter ref="A2:I46"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3480,7 +3506,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3495,39 +3521,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3553,17 +3579,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3571,134 +3597,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3706,10 +3732,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3717,56 +3743,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$46</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$47</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="190">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -396,6 +396,9 @@
   </si>
   <si>
     <t>2026-09-28T01:59:30.329228Z</t>
+  </si>
+  <si>
+    <t>2026-09-28T08:57:53.453390Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2290,7 +2293,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I46"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3483,8 +3486,31 @@
         <v>587.1799999999999</v>
       </c>
     </row>
+    <row r="47" spans="1:9">
+      <c r="A47" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="4"/>
+      <c r="C47" s="4"/>
+      <c r="D47" s="4"/>
+      <c r="E47" s="6">
+        <v>1761.186889648438</v>
+      </c>
+      <c r="F47" s="6">
+        <v>0.3441854119300842</v>
+      </c>
+      <c r="G47" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H47" s="6">
+        <v>-4.38</v>
+      </c>
+      <c r="I47" s="6">
+        <v>550.13</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I46"/>
+  <autoFilter ref="A2:I47"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3506,7 +3532,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3521,39 +3547,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3579,17 +3605,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3597,134 +3623,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>146</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3732,10 +3758,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3743,56 +3769,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="191">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -399,6 +399,9 @@
   </si>
   <si>
     <t>2026-09-28T08:57:53.453390Z</t>
+  </si>
+  <si>
+    <t>2026-09-28T17:49:28.550564Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2293,7 +2296,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3509,8 +3512,31 @@
         <v>550.13</v>
       </c>
     </row>
+    <row r="48" spans="1:9">
+      <c r="A48" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B48" s="4"/>
+      <c r="C48" s="4"/>
+      <c r="D48" s="4"/>
+      <c r="E48" s="6">
+        <v>3969.695556640625</v>
+      </c>
+      <c r="F48" s="6">
+        <v>11.56942653656006</v>
+      </c>
+      <c r="G48" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H48" s="6">
+        <v>-8.49</v>
+      </c>
+      <c r="I48" s="6">
+        <v>553.47</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I47"/>
+  <autoFilter ref="A2:I48"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3532,7 +3558,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3547,39 +3573,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3605,17 +3631,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3623,134 +3649,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3758,10 +3784,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3769,56 +3795,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$49</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="192">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>2026-09-28T17:49:28.550564Z</t>
+  </si>
+  <si>
+    <t>2026-09-28T23:31:00.557331Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2296,7 +2299,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3535,8 +3538,33 @@
         <v>553.47</v>
       </c>
     </row>
+    <row r="49" spans="1:9">
+      <c r="A49" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="B49" s="6">
+        <v>1</v>
+      </c>
+      <c r="C49" s="4"/>
+      <c r="D49" s="4"/>
+      <c r="E49" s="6">
+        <v>1707.258056640625</v>
+      </c>
+      <c r="F49" s="6">
+        <v>11.69964694976807</v>
+      </c>
+      <c r="G49" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H49" s="6">
+        <v>-10.49</v>
+      </c>
+      <c r="I49" s="6">
+        <v>598.27</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I48"/>
+  <autoFilter ref="A2:I49"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3558,7 +3586,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3573,39 +3601,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3631,17 +3659,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3649,134 +3677,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>148</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3784,10 +3812,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3795,56 +3823,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="193">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>2026-09-28T23:31:00.557331Z</t>
+  </si>
+  <si>
+    <t>2026-09-29T02:47:38.701656Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2299,7 +2302,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I49"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3563,8 +3566,37 @@
         <v>598.27</v>
       </c>
     </row>
+    <row r="50" spans="1:9">
+      <c r="A50" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B50" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="C50" s="6">
+        <v>0.43</v>
+      </c>
+      <c r="D50" s="6">
+        <v>327.8</v>
+      </c>
+      <c r="E50" s="6">
+        <v>1144.322631835938</v>
+      </c>
+      <c r="F50" s="6">
+        <v>1.25614333152771</v>
+      </c>
+      <c r="G50" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H50" s="6">
+        <v>-10.31</v>
+      </c>
+      <c r="I50" s="6">
+        <v>671.6900000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I49"/>
+  <autoFilter ref="A2:I50"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3586,7 +3618,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3601,39 +3633,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3659,17 +3691,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3677,134 +3709,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>149</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3812,10 +3844,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3823,56 +3855,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="194">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -408,6 +408,9 @@
   </si>
   <si>
     <t>2026-09-29T02:47:38.701656Z</t>
+  </si>
+  <si>
+    <t>2026-09-29T10:08:35.860180Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2302,7 +2305,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I50"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3595,8 +3598,37 @@
         <v>671.6900000000001</v>
       </c>
     </row>
+    <row r="51" spans="1:9">
+      <c r="A51" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="B51" s="6">
+        <v>0.67</v>
+      </c>
+      <c r="C51" s="6">
+        <v>-1.36</v>
+      </c>
+      <c r="D51" s="6">
+        <v>310.98</v>
+      </c>
+      <c r="E51" s="6">
+        <v>2006.600952148438</v>
+      </c>
+      <c r="F51" s="6">
+        <v>0.3265899121761322</v>
+      </c>
+      <c r="G51" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H51" s="6">
+        <v>-10.22</v>
+      </c>
+      <c r="I51" s="6">
+        <v>673.61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I50"/>
+  <autoFilter ref="A2:I51"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3618,7 +3650,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3633,39 +3665,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3691,17 +3723,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3709,134 +3741,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>150</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3844,10 +3876,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3855,56 +3887,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$52</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="195">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -411,6 +411,9 @@
   </si>
   <si>
     <t>2026-09-29T10:08:35.860180Z</t>
+  </si>
+  <si>
+    <t>2026-09-29T16:38:57.224651Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2305,7 +2308,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3627,8 +3630,31 @@
         <v>673.61</v>
       </c>
     </row>
+    <row r="52" spans="1:9">
+      <c r="A52" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B52" s="4"/>
+      <c r="C52" s="4"/>
+      <c r="D52" s="4"/>
+      <c r="E52" s="6">
+        <v>5599.37646484375</v>
+      </c>
+      <c r="F52" s="6">
+        <v>8.392133712768555</v>
+      </c>
+      <c r="G52" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H52" s="6">
+        <v>-10.22</v>
+      </c>
+      <c r="I52" s="6">
+        <v>673.61</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I51"/>
+  <autoFilter ref="A2:I52"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3650,7 +3676,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3665,39 +3691,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3723,17 +3749,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3741,134 +3767,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>151</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3876,10 +3902,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3887,56 +3913,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$53</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="196">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -414,6 +414,9 @@
   </si>
   <si>
     <t>2026-09-29T16:38:57.224651Z</t>
+  </si>
+  <si>
+    <t>2026-09-29T21:03:16.510548Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2308,7 +2311,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3653,8 +3656,31 @@
         <v>673.61</v>
       </c>
     </row>
+    <row r="53" spans="1:9">
+      <c r="A53" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="B53" s="4"/>
+      <c r="C53" s="4"/>
+      <c r="D53" s="4"/>
+      <c r="E53" s="6">
+        <v>3036.486328125</v>
+      </c>
+      <c r="F53" s="6">
+        <v>30.57290077209473</v>
+      </c>
+      <c r="G53" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H53" s="6">
+        <v>-9.92</v>
+      </c>
+      <c r="I53" s="6">
+        <v>679.49</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I52"/>
+  <autoFilter ref="A2:I53"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3676,7 +3702,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3691,39 +3717,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3749,17 +3775,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3767,134 +3793,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>152</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3902,10 +3928,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3913,56 +3939,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$53</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$54</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="197">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -417,6 +417,9 @@
   </si>
   <si>
     <t>2026-09-29T21:03:16.510548Z</t>
+  </si>
+  <si>
+    <t>2026-09-30T00:46:21.138590Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2311,7 +2314,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I53"/>
+  <dimension ref="A1:I54"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3679,8 +3682,31 @@
         <v>679.49</v>
       </c>
     </row>
+    <row r="54" spans="1:9">
+      <c r="A54" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B54" s="4"/>
+      <c r="C54" s="4"/>
+      <c r="D54" s="4"/>
+      <c r="E54" s="6">
+        <v>559.50146484375</v>
+      </c>
+      <c r="F54" s="6">
+        <v>0.6881929039955139</v>
+      </c>
+      <c r="G54" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H54" s="6">
+        <v>-9.859999999999999</v>
+      </c>
+      <c r="I54" s="6">
+        <v>680.3200000000001</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I53"/>
+  <autoFilter ref="A2:I54"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3702,7 +3728,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3717,39 +3743,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3775,17 +3801,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3793,134 +3819,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>153</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3928,10 +3954,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3939,56 +3965,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="198">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -420,6 +420,9 @@
   </si>
   <si>
     <t>2026-09-30T00:46:21.138590Z</t>
+  </si>
+  <si>
+    <t>2026-09-30T07:27:42.856534Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2314,7 +2317,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I54"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3705,8 +3708,35 @@
         <v>680.3200000000001</v>
       </c>
     </row>
+    <row r="55" spans="1:9">
+      <c r="A55" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="B55" s="4"/>
+      <c r="C55" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="D55" s="6">
+        <v>302.94</v>
+      </c>
+      <c r="E55" s="6">
+        <v>736.9383544921875</v>
+      </c>
+      <c r="F55" s="6">
+        <v>0.2321078777313232</v>
+      </c>
+      <c r="G55" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H55" s="6">
+        <v>-9.57</v>
+      </c>
+      <c r="I55" s="6">
+        <v>607.02</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I54"/>
+  <autoFilter ref="A2:I55"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3728,7 +3758,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3743,39 +3773,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3801,17 +3831,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3819,134 +3849,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3954,10 +3984,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3965,56 +3995,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$56</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="199">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -423,6 +423,9 @@
   </si>
   <si>
     <t>2026-09-30T07:27:42.856534Z</t>
+  </si>
+  <si>
+    <t>2026-09-30T19:38:02.012829Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2317,7 +2320,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I55"/>
+  <dimension ref="A1:I56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3735,8 +3738,31 @@
         <v>607.02</v>
       </c>
     </row>
+    <row r="56" spans="1:9">
+      <c r="A56" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B56" s="4"/>
+      <c r="C56" s="4"/>
+      <c r="D56" s="4"/>
+      <c r="E56" s="6">
+        <v>1297.184814453125</v>
+      </c>
+      <c r="F56" s="6">
+        <v>18.62481307983398</v>
+      </c>
+      <c r="G56" s="6">
+        <v>1.67</v>
+      </c>
+      <c r="H56" s="6">
+        <v>-9.609999999999999</v>
+      </c>
+      <c r="I56" s="6">
+        <v>586.5</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I55"/>
+  <autoFilter ref="A2:I56"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3758,7 +3784,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3773,39 +3799,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3831,17 +3857,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3849,134 +3875,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>155</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -3984,10 +4010,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -3995,56 +4021,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
+++ b/docs/data/satellite-risk/monthly/2026-09_Satellite_Anomaly_SpaceWeather.xlsx
@@ -14,14 +14,14 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Anomaly_Events!$A$3:$X$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$56</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Environment_Log!$A$2:$I$57</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="200">
   <si>
     <t>SWIFT Satellite Anomaly × Space Weather — 2026-09</t>
   </si>
@@ -426,6 +426,9 @@
   </si>
   <si>
     <t>2026-09-30T19:38:02.012829Z</t>
+  </si>
+  <si>
+    <t>2026-09-30T23:12:55.370219Z</t>
   </si>
   <si>
     <t>NCEI Legacy Spacecraft Anomaly Reference</t>
@@ -2320,7 +2323,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I57"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.7109375" customWidth="1"/>
@@ -3761,8 +3764,31 @@
         <v>586.5</v>
       </c>
     </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B57" s="4"/>
+      <c r="C57" s="4"/>
+      <c r="D57" s="4"/>
+      <c r="E57" s="6">
+        <v>777.345458984375</v>
+      </c>
+      <c r="F57" s="6">
+        <v>13.97785758972168</v>
+      </c>
+      <c r="G57" s="6">
+        <v>1.33</v>
+      </c>
+      <c r="H57" s="6">
+        <v>-9.470000000000001</v>
+      </c>
+      <c r="I57" s="6">
+        <v>556.04</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:I56"/>
+  <autoFilter ref="A2:I57"/>
   <mergeCells count="1">
     <mergeCell ref="A1:I1"/>
   </mergeCells>
@@ -3784,7 +3810,7 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3799,39 +3825,39 @@
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>25</v>
@@ -3857,17 +3883,17 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>24</v>
@@ -3875,134 +3901,134 @@
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>156</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" s="12" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -4010,10 +4036,10 @@
         <v>55</v>
       </c>
       <c r="B18" s="14" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -4021,56 +4047,56 @@
         <v>30</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B20" s="16" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" s="17" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" s="17" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" s="17" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
     </row>
     <row r="27" spans="1:3">
       <c r="A27" s="17" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" s="17" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="29" spans="1:3">
       <c r="A29" s="17" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
   </sheetData>
